--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1265.49</v>
+        <v>1321.38</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>2007.07</v>
+        <v>2095.7</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4803.72</v>
+        <v>5015.86</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>779.9400000000001</v>
+        <v>814.38</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2401.86</v>
+        <v>2507.93</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1886.84</v>
+        <v>1970.16</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1903.57</v>
+        <v>1987.63</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>1386.35</v>
+        <v>1447.58</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1415.08</v>
+        <v>1477.57</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1189.4</v>
+        <v>1241.93</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2909.87</v>
+        <v>3038.37</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2954.93</v>
+        <v>3085.43</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1682.15</v>
+        <v>1756.44</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1185.28</v>
+        <v>1237.62</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5600.72</v>
+        <v>5848.06</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>1353.15</v>
+        <v>1412.91</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>851.98</v>
+        <v>889.6</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>20132.04</v>
+        <v>21021.11</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1301.83</v>
+        <v>1359.32</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>3025.91</v>
+        <v>3159.54</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>2067.54</v>
+        <v>2158.84</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3109.48</v>
+        <v>3246.8</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>892.6</v>
+        <v>932.02</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8439.32</v>
+        <v>8812.01</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2740.61</v>
+        <v>2861.64</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3040.28</v>
+        <v>3174.55</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>804.3099999999999</v>
+        <v>839.83</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6712.44</v>
+        <v>6907.41</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>775.13</v>
+        <v>797.65</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>27506.59</v>
+        <v>28305.56</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>4183.08</v>
+        <v>4304.58</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>909.11</v>
+        <v>935.52</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>868.53</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>25194.45</v>
+        <v>25926.26</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>807.92</v>
+        <v>831.39</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>779.8099999999999</v>
+        <v>802.46</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>902.5599999999999</v>
+        <v>928.77</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2656.89</v>
+        <v>2734.06</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>31989.65</v>
+        <v>32918.83</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>7679.31</v>
+        <v>7902.37</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7544.2</v>
+        <v>7763.33</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2165.01</v>
+        <v>2227.89</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5699.58</v>
+        <v>5865.14</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>7568.08</v>
+        <v>7787.9</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>7239.75</v>
+        <v>7450.04</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10647.18</v>
+        <v>10956.44</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1189.11</v>
+        <v>1223.65</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>780.13</v>
+        <v>802.79</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1613.24</v>
+        <v>1660.1</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2830.3</v>
+        <v>2912.51</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1528.54</v>
+        <v>1534.57</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1043.83</v>
+        <v>1047.94</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3922.76</v>
+        <v>3938.22</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4344.34</v>
+        <v>4361.46</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>878.86</v>
+        <v>882.33</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2847.11</v>
+        <v>2858.34</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>11993.63</v>
+        <v>12040.92</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2038.51</v>
+        <v>2046.54</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1186.07</v>
+        <v>1190.75</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1386.97</v>
+        <v>1392.44</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>4188.42</v>
+        <v>4204.94</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1569.28</v>
+        <v>1575.47</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5293.38</v>
+        <v>5314.24</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2067.31</v>
+        <v>2075.46</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4312.08</v>
+        <v>4329.08</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2497.72</v>
+        <v>2507.57</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3279.09</v>
+        <v>3292.02</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1055.38</v>
+        <v>1059.54</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>983.86</v>
+        <v>987.74</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>9764.34</v>
+        <v>9802.83</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>4438.12</v>
+        <v>4455.62</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>2712.56</v>
+        <v>2723.26</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>13061.19</v>
+        <v>13112.68</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>1193.38</v>
+        <v>1198.09</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>767.13</v>
+        <v>770.16</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>967.55</v>
+        <v>971.36</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1327.74</v>
+        <v>1332.97</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>5849.86</v>
+        <v>5872.93</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1113.69</v>
+        <v>1118.08</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>53471.01</v>
+        <v>53681.83</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3262.06</v>
+        <v>3315.82</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8275.469999999999</v>
+        <v>8411.860000000001</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>6255.95</v>
+        <v>6359.06</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1057.29</v>
+        <v>1074.71</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1363.83</v>
+        <v>1386.31</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>936.9299999999999</v>
+        <v>952.37</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>958</v>
+        <v>973.79</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1229.43</v>
+        <v>1249.7</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>2225.9</v>
+        <v>2262.59</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1964.12</v>
+        <v>1996.49</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>792.72</v>
+        <v>805.79</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>6879.27</v>
+        <v>6992.65</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1247.55</v>
+        <v>1268.12</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1117.56</v>
+        <v>1135.98</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2768.84</v>
+        <v>2814.47</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>21719.68</v>
+        <v>22077.65</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2398.72</v>
+        <v>2438.26</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3461.37</v>
+        <v>3518.42</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1149.36</v>
+        <v>1168.3</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>1054.62</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>2222.01</v>
+        <v>2258.63</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>11770.56</v>
+        <v>11964.56</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1807.69</v>
+        <v>1837.48</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>10396.43</v>
+        <v>10567.78</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>8085.1</v>
+        <v>8218.360000000001</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1879.74</v>
+        <v>1910.72</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2006.26</v>
+        <v>2039.33</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>4838.17</v>
+        <v>4917.91</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>932.23</v>
+        <v>947.59</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>1808.46</v>
+        <v>1838.26</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>778.73</v>
+        <v>791.5700000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>1693.66</v>
+        <v>1721.57</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>4809.6</v>
+        <v>4888.87</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>7647.08</v>
+        <v>7773.12</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>822.45</v>
+        <v>836</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>1876.1</v>
+        <v>1907.03</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2857.62</v>
+        <v>2904.72</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>2297.28</v>
+        <v>2302.93</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6116.16</v>
+        <v>6131.21</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>1700.38</v>
+        <v>1704.57</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>1365.35</v>
+        <v>1368.71</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>929.75</v>
+        <v>932.04</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3489.84</v>
+        <v>3498.43</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>3331.05</v>
+        <v>3339.24</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>987.95</v>
+        <v>990.38</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2434.16</v>
+        <v>2440.15</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>3403.46</v>
+        <v>3411.83</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>3045.32</v>
+        <v>3052.81</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3917.61</v>
+        <v>3927.25</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1774.89</v>
+        <v>1779.26</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1753.3</v>
+        <v>1757.61</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1851.25</v>
+        <v>1855.81</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>1253.75</v>
+        <v>1256.83</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>883.92</v>
+        <v>886.1</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>938.51</v>
+        <v>940.8200000000001</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>2971.95</v>
+        <v>2979.26</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2216.73</v>
+        <v>2222.19</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>4831.54</v>
+        <v>4843.42</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2427.1</v>
+        <v>2433.07</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1254.75</v>
+        <v>1257.83</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>2816.15</v>
+        <v>2823.08</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>7466.57</v>
+        <v>7484.94</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1444.15</v>
+        <v>1447.7</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>13229.27</v>
+        <v>13261.82</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1968.54</v>
+        <v>1973.38</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>10666.42</v>
+        <v>10692.67</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>3316.37</v>
+        <v>3324.53</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>39297.39</v>
+        <v>39394.07</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>6293.42</v>
+        <v>6308.9</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2292.41</v>
+        <v>2298.05</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>3359.01</v>
+        <v>3367.28</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1400.85</v>
+        <v>1404.3</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4800.16</v>
+        <v>4811.97</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>1123.7</v>
+        <v>1126.47</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>44018.82</v>
+        <v>44127.12</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>1910.31</v>
+        <v>1915.01</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>776.6</v>
+        <v>778.51</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8806.01</v>
+        <v>8827.68</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>768.47</v>
+        <v>770.36</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>2437.84</v>
+        <v>2443.84</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>769.2</v>
+        <v>771.09</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>874.1</v>
+        <v>876.25</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>1567.58</v>
+        <v>1571.44</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>54694.11</v>
+        <v>53989.98</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1056.74</v>
+        <v>1043.13</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>783.01</v>
+        <v>772.9299999999999</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>4039.87</v>
+        <v>3987.86</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>1570.39</v>
+        <v>1550.17</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>805.5700000000001</v>
+        <v>795.1900000000001</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>845.72</v>
+        <v>834.83</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>825.87</v>
+        <v>815.24</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>3920.4</v>
+        <v>3869.93</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>2240.34</v>
+        <v>2211.5</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>3261.38</v>
+        <v>3219.39</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>784.71</v>
+        <v>774.61</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>811.1</v>
+        <v>800.66</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>9855.440000000001</v>
+        <v>9728.559999999999</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>1791.62</v>
+        <v>1768.55</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>3403.01</v>
+        <v>3359.2</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>2386.82</v>
+        <v>2356.09</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>2058.81</v>
+        <v>2032.31</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>1307.86</v>
+        <v>1291.02</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1885.39</v>
+        <v>1861.12</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4481.44</v>
+        <v>4423.75</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>4087.74</v>
+        <v>4035.11</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>8733.91</v>
+        <v>8621.469999999999</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>1472.48</v>
+        <v>1453.52</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>829.59</v>
+        <v>818.91</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2059.86</v>
+        <v>2033.34</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1276.88</v>
+        <v>1260.44</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2743.89</v>
+        <v>2708.57</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>872.75</v>
+        <v>861.51</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>765.65</v>
+        <v>755.8</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1549.46</v>
+        <v>1529.51</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>14402.39</v>
+        <v>14300.75</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1503.59</v>
+        <v>1492.98</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>4483.82</v>
+        <v>4452.18</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1558.3</v>
+        <v>1547.3</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>7188.57</v>
+        <v>7137.84</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>773.67</v>
+        <v>768.21</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2037.62</v>
+        <v>2023.24</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>34827.46</v>
+        <v>34581.68</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>8539.190000000001</v>
+        <v>8478.92</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>2546.99</v>
+        <v>2529.01</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>1269.57</v>
+        <v>1260.61</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>1121.61</v>
+        <v>1113.69</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2169.59</v>
+        <v>2154.27</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>803.28</v>
+        <v>797.61</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>923.59</v>
+        <v>917.08</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2801.54</v>
+        <v>2781.77</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>19127.24</v>
+        <v>18992.26</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2104.91</v>
+        <v>2090.06</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1573.03</v>
+        <v>1561.93</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1067.99</v>
+        <v>1060.45</v>
       </c>
     </row>
     <row r="216">
@@ -13627,7 +13627,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>126849.06</v>
+        <v>125953.88</v>
       </c>
     </row>
     <row r="217">
@@ -13688,7 +13688,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>7317.4</v>
+        <v>7265.76</v>
       </c>
     </row>
     <row r="218">
@@ -13749,7 +13749,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2501.26</v>
+        <v>2483.6</v>
       </c>
     </row>
     <row r="219">
@@ -13810,7 +13810,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>12267.05</v>
+        <v>12180.48</v>
       </c>
     </row>
     <row r="220">
@@ -13871,7 +13871,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>14423.7</v>
+        <v>14321.91</v>
       </c>
     </row>
     <row r="221">
@@ -13932,7 +13932,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1642.99</v>
+        <v>1631.4</v>
       </c>
     </row>
     <row r="222">
@@ -13993,7 +13993,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>1341.37</v>
+        <v>1331.91</v>
       </c>
     </row>
     <row r="223">
@@ -14054,7 +14054,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>1618.39</v>
+        <v>1606.97</v>
       </c>
     </row>
     <row r="224">
@@ -14115,7 +14115,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>1944.02</v>
+        <v>1930.3</v>
       </c>
     </row>
     <row r="225">
@@ -14176,7 +14176,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3857.87</v>
+        <v>3830.64</v>
       </c>
     </row>
     <row r="226">
@@ -14237,7 +14237,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1512.33</v>
+        <v>1501.66</v>
       </c>
     </row>
     <row r="227">
@@ -14298,7 +14298,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>4945.58</v>
+        <v>4910.68</v>
       </c>
     </row>
     <row r="228">
@@ -14359,7 +14359,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>1987.7</v>
+        <v>1973.68</v>
       </c>
     </row>
     <row r="229">
@@ -14420,7 +14420,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>14241.91</v>
+        <v>14141.4</v>
       </c>
     </row>
     <row r="230">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>20216.68</v>
+        <v>20074.01</v>
       </c>
     </row>
     <row r="231">
@@ -14542,7 +14542,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>803.73</v>
+        <v>798.0599999999999</v>
       </c>
     </row>
     <row r="232">
@@ -14603,7 +14603,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>924.58</v>
+        <v>918.0599999999999</v>
       </c>
     </row>
     <row r="233">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>1602.86</v>
+        <v>1591.54</v>
       </c>
     </row>
     <row r="234">
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2982.9</v>
+        <v>2961.85</v>
       </c>
     </row>
     <row r="235">
@@ -14786,7 +14786,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>3184.44</v>
+        <v>3161.97</v>
       </c>
     </row>
     <row r="236">
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>970.38</v>
+        <v>963.54</v>
       </c>
     </row>
     <row r="237">
@@ -14908,7 +14908,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3064.28</v>
+        <v>3042.66</v>
       </c>
     </row>
     <row r="238">
@@ -14969,7 +14969,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>1911.2</v>
+        <v>1897.71</v>
       </c>
     </row>
     <row r="239">
@@ -15030,7 +15030,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>5203.33</v>
+        <v>5166.61</v>
       </c>
     </row>
     <row r="240">
@@ -15091,7 +15091,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>45477.95</v>
+        <v>45157.01</v>
       </c>
     </row>
     <row r="241">
@@ -15152,7 +15152,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>1830.43</v>
+        <v>1817.52</v>
       </c>
     </row>
     <row r="242">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>924.74</v>
+        <v>918.21</v>
       </c>
     </row>
     <row r="243">
@@ -15274,7 +15274,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>5157.12</v>
+        <v>5120.73</v>
       </c>
     </row>
     <row r="244">
@@ -15335,7 +15335,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>2634.26</v>
+        <v>2615.67</v>
       </c>
     </row>
     <row r="245">
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>2794.97</v>
+        <v>2775.25</v>
       </c>
     </row>
     <row r="246">
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>1192.98</v>
+        <v>1184.57</v>
       </c>
     </row>
     <row r="247">
@@ -15518,7 +15518,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>2080.9</v>
+        <v>2066.21</v>
       </c>
     </row>
     <row r="248">
@@ -15579,7 +15579,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>4953.15</v>
+        <v>5042.96</v>
       </c>
     </row>
     <row r="249">
@@ -15640,7 +15640,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>2655.21</v>
+        <v>2703.35</v>
       </c>
     </row>
     <row r="250">
@@ -15701,7 +15701,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>8590.98</v>
+        <v>8746.74</v>
       </c>
     </row>
     <row r="251">
@@ -15762,7 +15762,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>1278.59</v>
+        <v>1301.78</v>
       </c>
     </row>
     <row r="252">
@@ -15823,7 +15823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1817.66</v>
+        <v>1850.62</v>
       </c>
     </row>
     <row r="253">
@@ -15884,7 +15884,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>1208.03</v>
+        <v>1229.93</v>
       </c>
     </row>
     <row r="254">
@@ -15945,7 +15945,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>770.62</v>
+        <v>784.59</v>
       </c>
     </row>
     <row r="255">
@@ -16006,7 +16006,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>1560.67</v>
+        <v>1588.97</v>
       </c>
     </row>
     <row r="256">
@@ -16067,7 +16067,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>1383.05</v>
+        <v>1408.12</v>
       </c>
     </row>
     <row r="257">
@@ -16128,7 +16128,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>4052.67</v>
+        <v>4126.15</v>
       </c>
     </row>
     <row r="258">
@@ -16189,7 +16189,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>1900.95</v>
+        <v>1935.42</v>
       </c>
     </row>
     <row r="259">
@@ -16250,7 +16250,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>1813.33</v>
+        <v>1846.21</v>
       </c>
     </row>
     <row r="260">
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>1256.77</v>
+        <v>1279.55</v>
       </c>
     </row>
     <row r="261">
@@ -16372,7 +16372,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>1119.59</v>
+        <v>1139.89</v>
       </c>
     </row>
     <row r="262">
@@ -16433,7 +16433,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>1199.29</v>
+        <v>1221.04</v>
       </c>
     </row>
     <row r="263">
@@ -16494,7 +16494,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>1002.62</v>
+        <v>1020.8</v>
       </c>
     </row>
     <row r="264">
@@ -16555,7 +16555,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>865.35</v>
+        <v>881.04</v>
       </c>
     </row>
     <row r="265">
@@ -16616,7 +16616,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>3484.76</v>
+        <v>3547.94</v>
       </c>
     </row>
     <row r="266">
@@ -16677,7 +16677,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1255.13</v>
+        <v>1277.89</v>
       </c>
     </row>
     <row r="267">
@@ -16738,7 +16738,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>912.8099999999999</v>
+        <v>929.36</v>
       </c>
     </row>
     <row r="268">
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>8254.030000000001</v>
+        <v>8403.690000000001</v>
       </c>
     </row>
     <row r="269">
@@ -16860,7 +16860,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>776.8</v>
+        <v>790.89</v>
       </c>
     </row>
     <row r="270">
@@ -16921,7 +16921,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1179.13</v>
+        <v>1200.51</v>
       </c>
     </row>
     <row r="271">
@@ -16982,7 +16982,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>7642.18</v>
+        <v>7780.74</v>
       </c>
     </row>
     <row r="272">
@@ -17043,7 +17043,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1734.08</v>
+        <v>1765.52</v>
       </c>
     </row>
     <row r="273">
@@ -17104,7 +17104,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>1189.68</v>
+        <v>1211.25</v>
       </c>
     </row>
     <row r="274">
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>4495.27</v>
+        <v>4576.77</v>
       </c>
     </row>
     <row r="275">
@@ -17226,7 +17226,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>2489.98</v>
+        <v>2535.12</v>
       </c>
     </row>
     <row r="276">
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1628.58</v>
+        <v>1658.11</v>
       </c>
     </row>
     <row r="277">
@@ -17348,7 +17348,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>11952.4</v>
+        <v>12169.11</v>
       </c>
     </row>
     <row r="278">
@@ -17409,7 +17409,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>7106.25</v>
+        <v>7235.09</v>
       </c>
     </row>
     <row r="279">
@@ -17470,7 +17470,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>841.02</v>
+        <v>856.27</v>
       </c>
     </row>
     <row r="280">
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>1497.27</v>
+        <v>1524.42</v>
       </c>
     </row>
     <row r="281">
@@ -17592,7 +17592,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>886.72</v>
+        <v>902.8</v>
       </c>
     </row>
     <row r="282">
@@ -17653,7 +17653,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2552.98</v>
+        <v>2599.26</v>
       </c>
     </row>
     <row r="283">
@@ -17714,7 +17714,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>8780.879999999999</v>
+        <v>8940.08</v>
       </c>
     </row>
     <row r="284">
@@ -17775,7 +17775,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>2348.23</v>
+        <v>2390.8</v>
       </c>
     </row>
     <row r="285">
@@ -17836,7 +17836,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>2191.61</v>
+        <v>2225.94</v>
       </c>
     </row>
     <row r="286">
@@ -17897,7 +17897,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>792.6</v>
+        <v>805.02</v>
       </c>
     </row>
     <row r="287">
@@ -17958,7 +17958,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>5940.17</v>
+        <v>6033.22</v>
       </c>
     </row>
     <row r="288">
@@ -18019,7 +18019,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>977.35</v>
+        <v>992.66</v>
       </c>
     </row>
     <row r="289">
@@ -18080,7 +18080,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>1063.33</v>
+        <v>1079.99</v>
       </c>
     </row>
     <row r="290">
@@ -18141,7 +18141,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>7062.37</v>
+        <v>7173</v>
       </c>
     </row>
     <row r="291">
@@ -18202,7 +18202,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>4883.07</v>
+        <v>4959.56</v>
       </c>
     </row>
     <row r="292">
@@ -18263,7 +18263,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>982.45</v>
+        <v>997.84</v>
       </c>
     </row>
     <row r="293">
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>15391.67</v>
+        <v>15632.77</v>
       </c>
     </row>
     <row r="294">
@@ -18385,7 +18385,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1984.26</v>
+        <v>2015.35</v>
       </c>
     </row>
     <row r="295">
@@ -18446,7 +18446,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1348.99</v>
+        <v>1370.12</v>
       </c>
     </row>
     <row r="296">
@@ -18507,7 +18507,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1900.42</v>
+        <v>1930.19</v>
       </c>
     </row>
     <row r="297">
@@ -18568,7 +18568,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>8553.34</v>
+        <v>8687.32</v>
       </c>
     </row>
     <row r="298">
@@ -18629,7 +18629,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>2375.11</v>
+        <v>2412.31</v>
       </c>
     </row>
     <row r="299">
@@ -18690,7 +18690,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>3450.69</v>
+        <v>3504.74</v>
       </c>
     </row>
     <row r="300">
@@ -18751,7 +18751,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>893.5700000000001</v>
+        <v>907.5700000000001</v>
       </c>
     </row>
     <row r="301">
@@ -18812,7 +18812,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>1038.67</v>
+        <v>1054.94</v>
       </c>
     </row>
     <row r="302">
@@ -18873,7 +18873,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>786.03</v>
+        <v>798.35</v>
       </c>
     </row>
     <row r="303">
@@ -18934,7 +18934,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>1086.96</v>
+        <v>1103.98</v>
       </c>
     </row>
     <row r="304">
@@ -18995,7 +18995,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>1426.82</v>
+        <v>1449.17</v>
       </c>
     </row>
     <row r="305">
@@ -19056,7 +19056,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>5224.44</v>
+        <v>5306.28</v>
       </c>
     </row>
     <row r="306">
@@ -19117,7 +19117,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>1966.78</v>
+        <v>1997.59</v>
       </c>
     </row>
     <row r="307">
@@ -19178,7 +19178,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>4178.62</v>
+        <v>4244.08</v>
       </c>
     </row>
     <row r="308">
@@ -19239,7 +19239,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>776.79</v>
+        <v>788.96</v>
       </c>
     </row>
     <row r="309">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1334.46</v>
+        <v>1355.36</v>
       </c>
     </row>
     <row r="310">
@@ -19361,7 +19361,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>788.0700000000001</v>
+        <v>800.42</v>
       </c>
     </row>
     <row r="311">
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>910.01</v>
+        <v>924.26</v>
       </c>
     </row>
     <row r="312">
@@ -19483,7 +19483,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>5643.62</v>
+        <v>5732.02</v>
       </c>
     </row>
     <row r="313">
@@ -19544,7 +19544,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>2895.68</v>
+        <v>2941.04</v>
       </c>
     </row>
     <row r="314">
@@ -19605,7 +19605,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>2480.07</v>
+        <v>2518.92</v>
       </c>
     </row>
     <row r="315">
@@ -19666,7 +19666,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3614.89</v>
+        <v>3671.51</v>
       </c>
     </row>
     <row r="316">
@@ -19727,7 +19727,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>19369.03</v>
+        <v>19368.03</v>
       </c>
     </row>
     <row r="317">
@@ -19788,7 +19788,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1401.77</v>
+        <v>1401.7</v>
       </c>
     </row>
     <row r="318">
@@ -19849,7 +19849,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>8344.17</v>
+        <v>8343.74</v>
       </c>
     </row>
     <row r="319">
@@ -19910,7 +19910,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>881.9</v>
+        <v>881.86</v>
       </c>
     </row>
     <row r="320">
@@ -19971,7 +19971,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>879.12</v>
+        <v>879.0700000000001</v>
       </c>
     </row>
     <row r="321">
@@ -20032,7 +20032,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2238.18</v>
+        <v>2238.07</v>
       </c>
     </row>
     <row r="322">
@@ -20093,7 +20093,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>4447.79</v>
+        <v>4447.56</v>
       </c>
     </row>
     <row r="323">
@@ -20154,7 +20154,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>7614.02</v>
+        <v>7613.63</v>
       </c>
     </row>
     <row r="324">
@@ -20215,7 +20215,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>976.8</v>
+        <v>976.75</v>
       </c>
     </row>
     <row r="325">
@@ -20276,7 +20276,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2601.12</v>
+        <v>2600.99</v>
       </c>
     </row>
     <row r="326">
@@ -20337,7 +20337,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>8558.059999999999</v>
+        <v>8557.610000000001</v>
       </c>
     </row>
     <row r="327">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>855.6</v>
+        <v>855.5599999999999</v>
       </c>
     </row>
     <row r="328">
@@ -20459,7 +20459,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1091.44</v>
+        <v>1091.38</v>
       </c>
     </row>
     <row r="329">
@@ -20520,7 +20520,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>13558.44</v>
+        <v>13557.74</v>
       </c>
     </row>
     <row r="330">
@@ -20581,7 +20581,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>10691.43</v>
+        <v>10690.88</v>
       </c>
     </row>
     <row r="331">
@@ -20642,7 +20642,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>891.8200000000001</v>
+        <v>891.77</v>
       </c>
     </row>
     <row r="332">
@@ -20703,7 +20703,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>3137.52</v>
+        <v>3137.36</v>
       </c>
     </row>
     <row r="333">
@@ -20764,7 +20764,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>13410.25</v>
+        <v>13409.56</v>
       </c>
     </row>
     <row r="334">
@@ -20825,7 +20825,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>2567.49</v>
+        <v>2567.35</v>
       </c>
     </row>
     <row r="335">
@@ -20886,7 +20886,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>1688.8</v>
+        <v>1688.71</v>
       </c>
     </row>
     <row r="336">
@@ -20947,7 +20947,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>5090.53</v>
+        <v>5090.27</v>
       </c>
     </row>
     <row r="337">
@@ -21008,7 +21008,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>2256.69</v>
+        <v>2256.57</v>
       </c>
     </row>
     <row r="338">
@@ -21069,7 +21069,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>1212.77</v>
+        <v>1212.7</v>
       </c>
     </row>
     <row r="339">
@@ -21130,7 +21130,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>6880.1</v>
+        <v>6879.74</v>
       </c>
     </row>
     <row r="340">
@@ -21191,7 +21191,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1002.69</v>
+        <v>1002.64</v>
       </c>
     </row>
     <row r="341">
@@ -21252,7 +21252,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>932.8099999999999</v>
+        <v>932.76</v>
       </c>
     </row>
     <row r="342">
@@ -21313,7 +21313,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>3478.11</v>
+        <v>3477.93</v>
       </c>
     </row>
     <row r="343">
@@ -21374,7 +21374,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>1757.65</v>
+        <v>1757.55</v>
       </c>
     </row>
     <row r="344">
@@ -21435,7 +21435,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5172.44</v>
+        <v>5172.17</v>
       </c>
     </row>
     <row r="345">
@@ -21496,7 +21496,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>912.45</v>
+        <v>912.4</v>
       </c>
     </row>
     <row r="346">
@@ -21557,7 +21557,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>871.88</v>
+        <v>871.83</v>
       </c>
     </row>
     <row r="347">
@@ -21618,7 +21618,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>1298.39</v>
+        <v>1298.33</v>
       </c>
     </row>
     <row r="348">
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>9869.459999999999</v>
+        <v>9868.950000000001</v>
       </c>
     </row>
     <row r="349">
@@ -21740,7 +21740,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>4701.37</v>
+        <v>4701.13</v>
       </c>
     </row>
     <row r="350">
@@ -21801,7 +21801,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>1006.78</v>
+        <v>1002.28</v>
       </c>
     </row>
     <row r="351">
@@ -21862,7 +21862,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>18117.79</v>
+        <v>18036.78</v>
       </c>
     </row>
     <row r="352">
@@ -21923,7 +21923,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>3286.42</v>
+        <v>3271.73</v>
       </c>
     </row>
     <row r="353">
@@ -21984,7 +21984,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>1294.77</v>
+        <v>1288.98</v>
       </c>
     </row>
     <row r="354">
@@ -22045,7 +22045,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>1211.51</v>
+        <v>1206.09</v>
       </c>
     </row>
     <row r="355">
@@ -22106,7 +22106,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>2174.29</v>
+        <v>2164.57</v>
       </c>
     </row>
     <row r="356">
@@ -22167,7 +22167,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>2249.49</v>
+        <v>2239.44</v>
       </c>
     </row>
     <row r="357">
@@ -22228,7 +22228,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>4058.47</v>
+        <v>4040.33</v>
       </c>
     </row>
     <row r="358">
@@ -22289,7 +22289,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>13908.94</v>
+        <v>13846.75</v>
       </c>
     </row>
     <row r="359">
@@ -22350,7 +22350,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>1218.88</v>
+        <v>1213.43</v>
       </c>
     </row>
     <row r="360">
@@ -22411,7 +22411,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>1802.89</v>
+        <v>1794.83</v>
       </c>
     </row>
     <row r="361">
@@ -22472,7 +22472,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1888.53</v>
+        <v>1880.08</v>
       </c>
     </row>
     <row r="362">
@@ -22533,7 +22533,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>1370.67</v>
+        <v>1364.54</v>
       </c>
     </row>
     <row r="363">
@@ -22594,7 +22594,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>1244.96</v>
+        <v>1239.39</v>
       </c>
     </row>
     <row r="364">
@@ -22655,7 +22655,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>825.9400000000001</v>
+        <v>822.25</v>
       </c>
     </row>
     <row r="365">
@@ -22716,7 +22716,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>3417.4</v>
+        <v>3402.12</v>
       </c>
     </row>
     <row r="366">
@@ -22777,7 +22777,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>10417.6</v>
+        <v>10371.01</v>
       </c>
     </row>
     <row r="367">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>775.5</v>
+        <v>772.03</v>
       </c>
     </row>
     <row r="368">
@@ -22899,7 +22899,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>2359.35</v>
+        <v>2348.8</v>
       </c>
     </row>
     <row r="369">
@@ -22960,7 +22960,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>2738.51</v>
+        <v>2726.27</v>
       </c>
     </row>
     <row r="370">
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>18875.75</v>
+        <v>18791.35</v>
       </c>
     </row>
     <row r="371">
@@ -23082,7 +23082,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>936.22</v>
+        <v>932.03</v>
       </c>
     </row>
     <row r="372">
@@ -23143,7 +23143,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>10979.63</v>
+        <v>10930.53</v>
       </c>
     </row>
     <row r="373">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>984.75</v>
+        <v>980.35</v>
       </c>
     </row>
     <row r="374">
@@ -23265,7 +23265,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>6971.15</v>
+        <v>6939.97</v>
       </c>
     </row>
     <row r="375">
@@ -23326,7 +23326,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>8225.530000000001</v>
+        <v>8232.620000000001</v>
       </c>
     </row>
     <row r="376">
@@ -23387,7 +23387,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>1779.8</v>
+        <v>1781.33</v>
       </c>
     </row>
     <row r="377">
@@ -23448,7 +23448,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>776.83</v>
+        <v>777.5</v>
       </c>
     </row>
     <row r="378">
@@ -23509,7 +23509,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>1756.8</v>
+        <v>1758.32</v>
       </c>
     </row>
     <row r="379">
@@ -23570,7 +23570,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>940.9</v>
+        <v>941.71</v>
       </c>
     </row>
     <row r="380">
@@ -23631,7 +23631,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>1553.72</v>
+        <v>1555.06</v>
       </c>
     </row>
     <row r="381">
@@ -23692,7 +23692,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>775.24</v>
+        <v>775.91</v>
       </c>
     </row>
     <row r="382">
@@ -23753,7 +23753,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>5367.53</v>
+        <v>5372.15</v>
       </c>
     </row>
     <row r="383">
@@ -23814,7 +23814,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>906.4400000000001</v>
+        <v>907.22</v>
       </c>
     </row>
     <row r="384">
@@ -23875,7 +23875,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>775.33</v>
+        <v>776</v>
       </c>
     </row>
     <row r="385">
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>6646.77</v>
+        <v>6652.5</v>
       </c>
     </row>
     <row r="386">
@@ -23997,7 +23997,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>2073.2</v>
+        <v>2074.98</v>
       </c>
     </row>
     <row r="387">
@@ -24058,7 +24058,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>822.4400000000001</v>
+        <v>823.15</v>
       </c>
     </row>
     <row r="388">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>1947.99</v>
+        <v>1949.66</v>
       </c>
     </row>
     <row r="389">
@@ -24180,7 +24180,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3999.05</v>
+        <v>4002.5</v>
       </c>
     </row>
     <row r="390">
@@ -24241,7 +24241,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1263.33</v>
+        <v>1264.42</v>
       </c>
     </row>
     <row r="391">
@@ -24302,7 +24302,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>4724.06</v>
+        <v>4728.13</v>
       </c>
     </row>
     <row r="392">
@@ -24363,7 +24363,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>803.59</v>
+        <v>804.29</v>
       </c>
     </row>
     <row r="393">
@@ -24424,7 +24424,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>818.2</v>
+        <v>818.91</v>
       </c>
     </row>
     <row r="394">
@@ -24485,7 +24485,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>1353.29</v>
+        <v>1354.46</v>
       </c>
     </row>
     <row r="395">
@@ -24546,7 +24546,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2379.29</v>
+        <v>2381.34</v>
       </c>
     </row>
     <row r="396">
@@ -24607,7 +24607,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>945.13</v>
+        <v>945.9400000000001</v>
       </c>
     </row>
     <row r="397">
@@ -24668,7 +24668,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>890.66</v>
+        <v>891.42</v>
       </c>
     </row>
     <row r="398">
@@ -24729,7 +24729,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2211.88</v>
+        <v>2213.78</v>
       </c>
     </row>
     <row r="399">
@@ -24790,7 +24790,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>10882.58</v>
+        <v>10891.95</v>
       </c>
     </row>
     <row r="400">
@@ -24851,7 +24851,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>1715.93</v>
+        <v>1717.41</v>
       </c>
     </row>
     <row r="401">
@@ -24912,7 +24912,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>1179.76</v>
+        <v>1180.77</v>
       </c>
     </row>
     <row r="402">
@@ -24973,7 +24973,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>2214.16</v>
+        <v>2216.06</v>
       </c>
     </row>
     <row r="403">
@@ -25034,7 +25034,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>14008.76</v>
+        <v>14020.83</v>
       </c>
     </row>
     <row r="404">
@@ -25095,7 +25095,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>47893.85</v>
+        <v>47935.11</v>
       </c>
     </row>
     <row r="405">
@@ -25156,7 +25156,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>2510.68</v>
+        <v>2512.84</v>
       </c>
     </row>
     <row r="406">
@@ -25217,7 +25217,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>771.5599999999999</v>
+        <v>772.23</v>
       </c>
     </row>
     <row r="407">
@@ -25278,7 +25278,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2399.62</v>
+        <v>2401.69</v>
       </c>
     </row>
     <row r="408">
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2546.4</v>
+        <v>2548.59</v>
       </c>
     </row>
     <row r="409">
@@ -25400,7 +25400,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1755.44</v>
+        <v>1756.96</v>
       </c>
     </row>
     <row r="410">
@@ -25461,7 +25461,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>11618.53</v>
+        <v>11628.54</v>
       </c>
     </row>
     <row r="411">
@@ -25522,7 +25522,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>6514.05</v>
+        <v>6519.67</v>
       </c>
     </row>
     <row r="412">
@@ -25583,7 +25583,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2298.36</v>
+        <v>2300.34</v>
       </c>
     </row>
     <row r="413">
@@ -25644,7 +25644,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>1981.91</v>
+        <v>1983.62</v>
       </c>
     </row>
     <row r="414">
@@ -25705,7 +25705,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>43835.2</v>
+        <v>43872.96</v>
       </c>
     </row>
     <row r="415">
@@ -25766,7 +25766,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>1160.72</v>
+        <v>1165.51</v>
       </c>
     </row>
     <row r="416">
@@ -25827,7 +25827,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>1775.2</v>
+        <v>1782.53</v>
       </c>
     </row>
     <row r="417">
@@ -25888,7 +25888,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>1386.22</v>
+        <v>1391.94</v>
       </c>
     </row>
     <row r="418">
@@ -25949,7 +25949,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>789.9400000000001</v>
+        <v>793.2</v>
       </c>
     </row>
     <row r="419">
@@ -26010,7 +26010,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>4584.52</v>
+        <v>4603.45</v>
       </c>
     </row>
     <row r="420">
@@ -26071,7 +26071,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>4486.7</v>
+        <v>4505.23</v>
       </c>
     </row>
     <row r="421">
@@ -26132,7 +26132,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>775.33</v>
+        <v>778.53</v>
       </c>
     </row>
     <row r="422">
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>2125.41</v>
+        <v>2134.18</v>
       </c>
     </row>
     <row r="423">
@@ -26254,7 +26254,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>974.9299999999999</v>
+        <v>978.96</v>
       </c>
     </row>
     <row r="424">
@@ -26315,7 +26315,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>2508.38</v>
+        <v>2518.75</v>
       </c>
     </row>
     <row r="425">
@@ -26376,7 +26376,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>771.21</v>
+        <v>774.4</v>
       </c>
     </row>
     <row r="426">
@@ -26437,7 +26437,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>1134.69</v>
+        <v>1139.37</v>
       </c>
     </row>
     <row r="427">
@@ -26498,7 +26498,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>3773</v>
+        <v>3788.59</v>
       </c>
     </row>
     <row r="428">
@@ -26559,7 +26559,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>822.88</v>
+        <v>826.28</v>
       </c>
     </row>
     <row r="429">
@@ -26620,7 +26620,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>1425.94</v>
+        <v>1431.83</v>
       </c>
     </row>
     <row r="430">
@@ -26681,7 +26681,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>780.66</v>
+        <v>783.89</v>
       </c>
     </row>
     <row r="431">
@@ -26742,7 +26742,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>931.1900000000001</v>
+        <v>935.03</v>
       </c>
     </row>
     <row r="432">
@@ -26803,7 +26803,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1739.91</v>
+        <v>1747.09</v>
       </c>
     </row>
     <row r="433">
@@ -26864,7 +26864,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>776.78</v>
+        <v>779.99</v>
       </c>
     </row>
     <row r="434">
@@ -26925,7 +26925,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>1188.26</v>
+        <v>1193.16</v>
       </c>
     </row>
     <row r="435">
@@ -26986,7 +26986,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>4014.52</v>
+        <v>4031.11</v>
       </c>
     </row>
     <row r="436">
@@ -27047,7 +27047,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>3211.99</v>
+        <v>3225.26</v>
       </c>
     </row>
     <row r="437">
@@ -27108,7 +27108,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>3615.25</v>
+        <v>3630.18</v>
       </c>
     </row>
     <row r="438">
@@ -27169,7 +27169,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>865.62</v>
+        <v>869.2</v>
       </c>
     </row>
     <row r="439">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>5245.9</v>
+        <v>5267.57</v>
       </c>
     </row>
     <row r="440">
@@ -27291,7 +27291,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>3804.26</v>
+        <v>3819.98</v>
       </c>
     </row>
     <row r="441">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>1059.21</v>
+        <v>1063.59</v>
       </c>
     </row>
     <row r="442">
@@ -27413,7 +27413,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>1093.77</v>
+        <v>1098.29</v>
       </c>
     </row>
     <row r="443">
@@ -27474,7 +27474,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>5439.98</v>
+        <v>5462.46</v>
       </c>
     </row>
     <row r="444">
@@ -27535,7 +27535,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>2631.29</v>
+        <v>2642.16</v>
       </c>
     </row>
     <row r="445">
@@ -27596,7 +27596,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>857.6900000000001</v>
+        <v>861.23</v>
       </c>
     </row>
     <row r="446">
@@ -27657,7 +27657,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>1500.13</v>
+        <v>1506.33</v>
       </c>
     </row>
     <row r="447">
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2180.3</v>
+        <v>2189.3</v>
       </c>
     </row>
     <row r="448">
@@ -27779,7 +27779,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>1534.36</v>
+        <v>1540.7</v>
       </c>
     </row>
     <row r="449">
@@ -27840,7 +27840,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>929.11</v>
+        <v>932.95</v>
       </c>
     </row>
     <row r="450">
@@ -27901,7 +27901,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>4488.4</v>
+        <v>4506.94</v>
       </c>
     </row>
     <row r="451">
@@ -27962,7 +27962,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>20167.36</v>
+        <v>20250.67</v>
       </c>
     </row>
     <row r="452">
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>5792.58</v>
+        <v>5816.51</v>
       </c>
     </row>
     <row r="453">
@@ -28084,7 +28084,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>956.17</v>
+        <v>953.53</v>
       </c>
     </row>
     <row r="454">
@@ -28145,7 +28145,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>1201.19</v>
+        <v>1197.88</v>
       </c>
     </row>
     <row r="455">
@@ -28206,7 +28206,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2759.09</v>
+        <v>2751.48</v>
       </c>
     </row>
     <row r="456">
@@ -28267,7 +28267,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>1375.22</v>
+        <v>1371.43</v>
       </c>
     </row>
     <row r="457">
@@ -28328,7 +28328,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>2174.99</v>
+        <v>2168.99</v>
       </c>
     </row>
     <row r="458">
@@ -28389,7 +28389,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>3089.13</v>
+        <v>3080.61</v>
       </c>
     </row>
     <row r="459">
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>6782.1</v>
+        <v>6763.39</v>
       </c>
     </row>
     <row r="460">
@@ -28511,7 +28511,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>7786.75</v>
+        <v>7765.27</v>
       </c>
     </row>
     <row r="461">
@@ -28572,7 +28572,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>8682.870000000001</v>
+        <v>8658.92</v>
       </c>
     </row>
     <row r="462">
@@ -28633,7 +28633,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>3588.68</v>
+        <v>3578.78</v>
       </c>
     </row>
     <row r="463">
@@ -28694,7 +28694,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>1457.99</v>
+        <v>1453.96</v>
       </c>
     </row>
     <row r="464">
@@ -28755,7 +28755,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2967.65</v>
+        <v>2959.46</v>
       </c>
     </row>
     <row r="465">
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>3512.95</v>
+        <v>3503.26</v>
       </c>
     </row>
     <row r="466">
@@ -28877,7 +28877,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>7859.22</v>
+        <v>7837.54</v>
       </c>
     </row>
     <row r="467">
@@ -28938,7 +28938,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>829.23</v>
+        <v>826.9400000000001</v>
       </c>
     </row>
     <row r="468">
@@ -28999,7 +28999,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>13280.02</v>
+        <v>13243.39</v>
       </c>
     </row>
     <row r="469">
@@ -29060,7 +29060,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2527.67</v>
+        <v>2520.7</v>
       </c>
     </row>
     <row r="470">
@@ -29121,7 +29121,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>1091.17</v>
+        <v>1088.16</v>
       </c>
     </row>
     <row r="471">
@@ -29182,7 +29182,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>784.02</v>
+        <v>781.86</v>
       </c>
     </row>
     <row r="472">
@@ -29243,7 +29243,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>10202.77</v>
+        <v>10174.62</v>
       </c>
     </row>
     <row r="473">
@@ -29304,7 +29304,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>5559.65</v>
+        <v>5544.32</v>
       </c>
     </row>
     <row r="474">
@@ -29365,7 +29365,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>2793.22</v>
+        <v>2785.51</v>
       </c>
     </row>
     <row r="475">
@@ -29426,7 +29426,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>1063.97</v>
+        <v>1061.03</v>
       </c>
     </row>
     <row r="476">
@@ -29487,7 +29487,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>6404.58</v>
+        <v>6386.91</v>
       </c>
     </row>
     <row r="477">
@@ -29548,7 +29548,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>978.27</v>
+        <v>975.5700000000001</v>
       </c>
     </row>
     <row r="478">
@@ -29609,7 +29609,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>1350.57</v>
+        <v>1346.85</v>
       </c>
     </row>
     <row r="479">
@@ -29670,7 +29670,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>3576.96</v>
+        <v>3567.09</v>
       </c>
     </row>
     <row r="480">
@@ -29731,7 +29731,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>32704.66</v>
+        <v>32614.45</v>
       </c>
     </row>
     <row r="481">
@@ -29792,7 +29792,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>3324.52</v>
+        <v>3315.35</v>
       </c>
     </row>
     <row r="482">
@@ -29853,7 +29853,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>7086.97</v>
+        <v>7067.42</v>
       </c>
     </row>
     <row r="483">
@@ -29914,7 +29914,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>3238.88</v>
+        <v>3229.95</v>
       </c>
     </row>
     <row r="484">
@@ -29975,7 +29975,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>1997.85</v>
+        <v>1992.34</v>
       </c>
     </row>
     <row r="485">
@@ -30036,7 +30036,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>1515.58</v>
+        <v>1511.4</v>
       </c>
     </row>
     <row r="486">
@@ -30097,7 +30097,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>3157.43</v>
+        <v>3148.72</v>
       </c>
     </row>
     <row r="487">
@@ -30158,7 +30158,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>3295.85</v>
+        <v>3286.76</v>
       </c>
     </row>
     <row r="488">
@@ -30219,7 +30219,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2891.84</v>
+        <v>2883.87</v>
       </c>
     </row>
     <row r="489">
@@ -30280,7 +30280,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>4026</v>
+        <v>4014.9</v>
       </c>
     </row>
     <row r="490">
@@ -30341,7 +30341,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1118.21</v>
+        <v>1115.12</v>
       </c>
     </row>
     <row r="491">
@@ -30402,7 +30402,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>4252.14</v>
+        <v>4240.41</v>
       </c>
     </row>
     <row r="492">
@@ -30463,7 +30463,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>2782.78</v>
+        <v>2775.11</v>
       </c>
     </row>
     <row r="493">
@@ -30524,7 +30524,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>1350.68</v>
+        <v>1335.09</v>
       </c>
     </row>
     <row r="494">
@@ -30585,7 +30585,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>3711.26</v>
+        <v>3668.42</v>
       </c>
     </row>
     <row r="495">
@@ -30646,7 +30646,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>74137.17</v>
+        <v>73281.31</v>
       </c>
     </row>
     <row r="496">
@@ -30707,7 +30707,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>866.17</v>
+        <v>856.17</v>
       </c>
     </row>
     <row r="497">
@@ -30768,7 +30768,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>2833.58</v>
+        <v>2800.87</v>
       </c>
     </row>
     <row r="498">
@@ -30829,7 +30829,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>888.22</v>
+        <v>877.97</v>
       </c>
     </row>
     <row r="499">
@@ -30890,7 +30890,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>1071.46</v>
+        <v>1059.09</v>
       </c>
     </row>
     <row r="500">
@@ -30951,7 +30951,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>1163.41</v>
+        <v>1149.98</v>
       </c>
     </row>
     <row r="501">
@@ -31012,7 +31012,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>1458.9</v>
+        <v>1442.06</v>
       </c>
     </row>
     <row r="502">
@@ -31073,7 +31073,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>2481.56</v>
+        <v>2452.91</v>
       </c>
     </row>
     <row r="503">
@@ -31134,7 +31134,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>6008.24</v>
+        <v>5938.88</v>
       </c>
     </row>
     <row r="504">
@@ -31195,7 +31195,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>1980.08</v>
+        <v>1957.22</v>
       </c>
     </row>
     <row r="505">
@@ -31256,7 +31256,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>9583.24</v>
+        <v>9472.610000000001</v>
       </c>
     </row>
     <row r="506">
@@ -31317,7 +31317,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2496.06</v>
+        <v>2467.24</v>
       </c>
     </row>
     <row r="507">
@@ -31378,7 +31378,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>4296.93</v>
+        <v>4247.32</v>
       </c>
     </row>
     <row r="508">
@@ -31439,7 +31439,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>3406.55</v>
+        <v>3367.22</v>
       </c>
     </row>
     <row r="509">
@@ -31500,7 +31500,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>4765.79</v>
+        <v>4710.77</v>
       </c>
     </row>
     <row r="510">
@@ -31561,7 +31561,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>2777.98</v>
+        <v>2745.91</v>
       </c>
     </row>
     <row r="511">
@@ -31622,7 +31622,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>1761.61</v>
+        <v>1741.28</v>
       </c>
     </row>
     <row r="512">
@@ -31683,7 +31683,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>3849.34</v>
+        <v>3804.91</v>
       </c>
     </row>
     <row r="513">
@@ -31744,7 +31744,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>1199.54</v>
+        <v>1185.7</v>
       </c>
     </row>
     <row r="514">
@@ -31805,7 +31805,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1216.3</v>
+        <v>1202.26</v>
       </c>
     </row>
     <row r="515">
@@ -31866,7 +31866,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1646.64</v>
+        <v>1627.63</v>
       </c>
     </row>
     <row r="516">
@@ -31927,7 +31927,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>3314.19</v>
+        <v>3275.93</v>
       </c>
     </row>
     <row r="517">
@@ -31988,7 +31988,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>3909.94</v>
+        <v>3864.8</v>
       </c>
     </row>
     <row r="518">
@@ -32049,7 +32049,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>768.4400000000001</v>
+        <v>759.5700000000001</v>
       </c>
     </row>
     <row r="519">
@@ -32110,7 +32110,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>2080.26</v>
+        <v>2056.24</v>
       </c>
     </row>
     <row r="520">
@@ -32171,7 +32171,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>1277.53</v>
+        <v>1262.78</v>
       </c>
     </row>
     <row r="521">
@@ -32232,7 +32232,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>9134</v>
+        <v>9028.549999999999</v>
       </c>
     </row>
     <row r="522">
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>3012.91</v>
+        <v>2978.13</v>
       </c>
     </row>
     <row r="523">
@@ -32354,7 +32354,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>2220.58</v>
+        <v>2194.94</v>
       </c>
     </row>
     <row r="524">
@@ -32415,7 +32415,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>1257.84</v>
+        <v>1239.08</v>
       </c>
     </row>
     <row r="525">
@@ -32476,7 +32476,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>1414.01</v>
+        <v>1392.92</v>
       </c>
     </row>
     <row r="526">
@@ -32537,7 +32537,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>896.21</v>
+        <v>882.85</v>
       </c>
     </row>
     <row r="527">
@@ -32598,7 +32598,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>2810.56</v>
+        <v>2768.64</v>
       </c>
     </row>
     <row r="528">
@@ -32659,7 +32659,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>1334.4</v>
+        <v>1314.5</v>
       </c>
     </row>
     <row r="529">
@@ -32720,7 +32720,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1688.18</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="530">
@@ -32781,7 +32781,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>771.62</v>
+        <v>760.11</v>
       </c>
     </row>
     <row r="531">
@@ -32842,7 +32842,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>1444.71</v>
+        <v>1423.16</v>
       </c>
     </row>
     <row r="532">
@@ -32903,7 +32903,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>4394.51</v>
+        <v>4328.97</v>
       </c>
     </row>
     <row r="533">
@@ -32964,7 +32964,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>1616.77</v>
+        <v>1592.65</v>
       </c>
     </row>
     <row r="534">
@@ -33025,7 +33025,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>3983.9</v>
+        <v>3924.48</v>
       </c>
     </row>
     <row r="535">
@@ -33086,7 +33086,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>5324.89</v>
+        <v>5245.47</v>
       </c>
     </row>
     <row r="536">
@@ -33147,7 +33147,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>964.95</v>
+        <v>950.5599999999999</v>
       </c>
     </row>
     <row r="537">
@@ -33208,7 +33208,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>2417.68</v>
+        <v>2381.62</v>
       </c>
     </row>
     <row r="538">
@@ -33269,7 +33269,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>5745.9</v>
+        <v>5660.2</v>
       </c>
     </row>
     <row r="539">
@@ -33330,7 +33330,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>968.8200000000001</v>
+        <v>954.37</v>
       </c>
     </row>
     <row r="540">
@@ -33391,7 +33391,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>2311.89</v>
+        <v>2277.41</v>
       </c>
     </row>
     <row r="541">
@@ -33452,7 +33452,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>3555.25</v>
+        <v>3502.22</v>
       </c>
     </row>
     <row r="542">
@@ -33513,7 +33513,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>3226</v>
+        <v>3177.88</v>
       </c>
     </row>
     <row r="543">
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>3210.33</v>
+        <v>3162.44</v>
       </c>
     </row>
     <row r="544">
@@ -33635,7 +33635,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>895.87</v>
+        <v>882.5</v>
       </c>
     </row>
     <row r="545">
@@ -33696,7 +33696,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>782.6900000000001</v>
+        <v>771.02</v>
       </c>
     </row>
     <row r="546">
@@ -33757,7 +33757,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>2857.65</v>
+        <v>2815.03</v>
       </c>
     </row>
     <row r="547">
@@ -33818,7 +33818,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>3296.29</v>
+        <v>3247.13</v>
       </c>
     </row>
     <row r="548">
@@ -33879,7 +33879,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>2659.5</v>
+        <v>2619.84</v>
       </c>
     </row>
     <row r="549">
@@ -33940,7 +33940,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>1748.72</v>
+        <v>1738.68</v>
       </c>
     </row>
     <row r="550">
@@ -34001,7 +34001,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>9418.280000000001</v>
+        <v>9364.18</v>
       </c>
     </row>
     <row r="551">
@@ -34062,7 +34062,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>1709.97</v>
+        <v>1700.15</v>
       </c>
     </row>
     <row r="552">
@@ -34123,7 +34123,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>1648.54</v>
+        <v>1639.07</v>
       </c>
     </row>
     <row r="553">
@@ -34184,7 +34184,7 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>32858.09</v>
+        <v>32669.34</v>
       </c>
     </row>
     <row r="554">
@@ -34245,7 +34245,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>5329.81</v>
+        <v>5299.2</v>
       </c>
     </row>
     <row r="555">
@@ -34306,7 +34306,7 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>769.01</v>
+        <v>764.6</v>
       </c>
     </row>
     <row r="556">
@@ -34367,7 +34367,7 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>1640.37</v>
+        <v>1630.94</v>
       </c>
     </row>
     <row r="557">
@@ -34428,7 +34428,7 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>1882.06</v>
+        <v>1871.25</v>
       </c>
     </row>
     <row r="558">
@@ -34489,7 +34489,7 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>2489.99</v>
+        <v>2475.68</v>
       </c>
     </row>
     <row r="559">
@@ -34550,7 +34550,7 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>1259</v>
+        <v>1251.76</v>
       </c>
     </row>
     <row r="560">
@@ -34611,7 +34611,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>2285.07</v>
+        <v>2271.94</v>
       </c>
     </row>
     <row r="561">
@@ -34672,7 +34672,7 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>1875.45</v>
+        <v>1864.68</v>
       </c>
     </row>
     <row r="562">
@@ -34733,7 +34733,7 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>873.77</v>
+        <v>868.75</v>
       </c>
     </row>
     <row r="563">
@@ -34794,7 +34794,7 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>3463.43</v>
+        <v>3443.53</v>
       </c>
     </row>
     <row r="564">
@@ -34855,7 +34855,7 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>2288.99</v>
+        <v>2275.84</v>
       </c>
     </row>
     <row r="565">
@@ -34916,7 +34916,7 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>7218.26</v>
+        <v>7176.8</v>
       </c>
     </row>
     <row r="566">
@@ -34977,7 +34977,7 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>2509.49</v>
+        <v>2495.08</v>
       </c>
     </row>
     <row r="567">
@@ -35038,7 +35038,7 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>1748.72</v>
+        <v>1738.68</v>
       </c>
     </row>
     <row r="568">
@@ -35099,7 +35099,7 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>2554.22</v>
+        <v>2539.55</v>
       </c>
     </row>
     <row r="569">
@@ -35160,7 +35160,7 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>854.08</v>
+        <v>849.1799999999999</v>
       </c>
     </row>
     <row r="570">
@@ -35221,7 +35221,7 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>848</v>
+        <v>843.13</v>
       </c>
     </row>
     <row r="571">
@@ -35282,7 +35282,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>1204.81</v>
+        <v>1197.89</v>
       </c>
     </row>
     <row r="572">
@@ -35343,7 +35343,7 @@
         </is>
       </c>
       <c r="M572" s="2" t="n">
-        <v>13726.5</v>
+        <v>13647.65</v>
       </c>
     </row>
     <row r="573">
@@ -35404,7 +35404,7 @@
         </is>
       </c>
       <c r="M573" s="2" t="n">
-        <v>4588.18</v>
+        <v>4561.83</v>
       </c>
     </row>
     <row r="574">
@@ -35465,7 +35465,7 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>7195.77</v>
+        <v>7154.43</v>
       </c>
     </row>
     <row r="575">
@@ -35526,7 +35526,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>5793.1</v>
+        <v>5759.83</v>
       </c>
     </row>
     <row r="576">
@@ -35587,7 +35587,7 @@
         </is>
       </c>
       <c r="M576" s="2" t="n">
-        <v>8061.82</v>
+        <v>8015.51</v>
       </c>
     </row>
     <row r="577">
@@ -35648,7 +35648,7 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>1567.11</v>
+        <v>1558.11</v>
       </c>
     </row>
     <row r="578">
@@ -35709,7 +35709,7 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>921.42</v>
+        <v>916.13</v>
       </c>
     </row>
     <row r="579">
@@ -35770,7 +35770,7 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>1872.84</v>
+        <v>1862.08</v>
       </c>
     </row>
     <row r="580">
@@ -35831,7 +35831,7 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>2817.48</v>
+        <v>2801.29</v>
       </c>
     </row>
     <row r="581">
@@ -35892,7 +35892,7 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>7925.92</v>
+        <v>7880.4</v>
       </c>
     </row>
     <row r="582">
@@ -35953,7 +35953,7 @@
         </is>
       </c>
       <c r="M582" s="2" t="n">
-        <v>34162.98</v>
+        <v>33966.74</v>
       </c>
     </row>
     <row r="583">
@@ -36014,7 +36014,7 @@
         </is>
       </c>
       <c r="M583" s="2" t="n">
-        <v>6774.18</v>
+        <v>6735.27</v>
       </c>
     </row>
     <row r="584">
@@ -36075,7 +36075,7 @@
         </is>
       </c>
       <c r="M584" s="2" t="n">
-        <v>972.99</v>
+        <v>967.4</v>
       </c>
     </row>
     <row r="585">
@@ -36136,7 +36136,7 @@
         </is>
       </c>
       <c r="M585" s="2" t="n">
-        <v>1114.49</v>
+        <v>1108.09</v>
       </c>
     </row>
     <row r="586">
@@ -36197,7 +36197,7 @@
         </is>
       </c>
       <c r="M586" s="2" t="n">
-        <v>1382.25</v>
+        <v>1374.31</v>
       </c>
     </row>
     <row r="587">
@@ -36258,7 +36258,7 @@
         </is>
       </c>
       <c r="M587" s="2" t="n">
-        <v>1999.46</v>
+        <v>1987.98</v>
       </c>
     </row>
     <row r="588">
@@ -36319,7 +36319,7 @@
         </is>
       </c>
       <c r="M588" s="2" t="n">
-        <v>2599.46</v>
+        <v>2584.53</v>
       </c>
     </row>
     <row r="589">
@@ -36380,7 +36380,7 @@
         </is>
       </c>
       <c r="M589" s="2" t="n">
-        <v>1374.82</v>
+        <v>1366.92</v>
       </c>
     </row>
     <row r="590">
@@ -36441,7 +36441,7 @@
         </is>
       </c>
       <c r="M590" s="2" t="n">
-        <v>23036.46</v>
+        <v>22888.88</v>
       </c>
     </row>
     <row r="591">
@@ -36502,7 +36502,7 @@
         </is>
       </c>
       <c r="M591" s="2" t="n">
-        <v>787.85</v>
+        <v>782.8</v>
       </c>
     </row>
     <row r="592">
@@ -36563,7 +36563,7 @@
         </is>
       </c>
       <c r="M592" s="2" t="n">
-        <v>1697.88</v>
+        <v>1687.01</v>
       </c>
     </row>
     <row r="593">
@@ -36624,7 +36624,7 @@
         </is>
       </c>
       <c r="M593" s="2" t="n">
-        <v>4345.87</v>
+        <v>4318.03</v>
       </c>
     </row>
     <row r="594">
@@ -36685,7 +36685,7 @@
         </is>
       </c>
       <c r="M594" s="2" t="n">
-        <v>2232.27</v>
+        <v>2217.96</v>
       </c>
     </row>
     <row r="595">
@@ -36746,7 +36746,7 @@
         </is>
       </c>
       <c r="M595" s="2" t="n">
-        <v>18776.74</v>
+        <v>18656.45</v>
       </c>
     </row>
     <row r="596">
@@ -36807,7 +36807,7 @@
         </is>
       </c>
       <c r="M596" s="2" t="n">
-        <v>1646.34</v>
+        <v>1635.8</v>
       </c>
     </row>
     <row r="597">
@@ -36868,7 +36868,7 @@
         </is>
       </c>
       <c r="M597" s="2" t="n">
-        <v>5364.26</v>
+        <v>5329.89</v>
       </c>
     </row>
     <row r="598">
@@ -36929,7 +36929,7 @@
         </is>
       </c>
       <c r="M598" s="2" t="n">
-        <v>1970.09</v>
+        <v>1957.47</v>
       </c>
     </row>
     <row r="599">
@@ -36990,7 +36990,7 @@
         </is>
       </c>
       <c r="M599" s="2" t="n">
-        <v>829.3200000000001</v>
+        <v>824.01</v>
       </c>
     </row>
     <row r="600">
@@ -37051,7 +37051,7 @@
         </is>
       </c>
       <c r="M600" s="2" t="n">
-        <v>1155.36</v>
+        <v>1147.95</v>
       </c>
     </row>
     <row r="601">
@@ -37112,7 +37112,7 @@
         </is>
       </c>
       <c r="M601" s="2" t="n">
-        <v>5476.21</v>
+        <v>5441.13</v>
       </c>
     </row>
     <row r="602">
@@ -37173,7 +37173,7 @@
         </is>
       </c>
       <c r="M602" s="2" t="n">
-        <v>3390.13</v>
+        <v>3368.41</v>
       </c>
     </row>
     <row r="603">
@@ -37234,7 +37234,7 @@
         </is>
       </c>
       <c r="M603" s="2" t="n">
-        <v>3610.33</v>
+        <v>3587.2</v>
       </c>
     </row>
     <row r="604">
@@ -37295,7 +37295,7 @@
         </is>
       </c>
       <c r="M604" s="2" t="n">
-        <v>2734.44</v>
+        <v>2716.93</v>
       </c>
     </row>
     <row r="605">
@@ -37356,7 +37356,7 @@
         </is>
       </c>
       <c r="M605" s="2" t="n">
-        <v>1274.55</v>
+        <v>1266.39</v>
       </c>
     </row>
     <row r="606">
@@ -37417,7 +37417,7 @@
         </is>
       </c>
       <c r="M606" s="2" t="n">
-        <v>1179.49</v>
+        <v>1171.93</v>
       </c>
     </row>
     <row r="607">
@@ -37478,7 +37478,7 @@
         </is>
       </c>
       <c r="M607" s="2" t="n">
-        <v>1266.24</v>
+        <v>1258.13</v>
       </c>
     </row>
     <row r="608">
@@ -37539,7 +37539,7 @@
         </is>
       </c>
       <c r="M608" s="2" t="n">
-        <v>1195.25</v>
+        <v>1187.59</v>
       </c>
     </row>
     <row r="609">
@@ -37600,7 +37600,7 @@
         </is>
       </c>
       <c r="M609" s="2" t="n">
-        <v>5518.57</v>
+        <v>5483.22</v>
       </c>
     </row>
     <row r="610">
@@ -37661,7 +37661,7 @@
         </is>
       </c>
       <c r="M610" s="2" t="n">
-        <v>9977.559999999999</v>
+        <v>9913.629999999999</v>
       </c>
     </row>
     <row r="611">
@@ -37722,7 +37722,7 @@
         </is>
       </c>
       <c r="M611" s="2" t="n">
-        <v>1618.13</v>
+        <v>1607.77</v>
       </c>
     </row>
     <row r="612">
@@ -37783,7 +37783,7 @@
         </is>
       </c>
       <c r="M612" s="2" t="n">
-        <v>2165.95</v>
+        <v>2152.07</v>
       </c>
     </row>
     <row r="613">
@@ -37844,7 +37844,7 @@
         </is>
       </c>
       <c r="M613" s="2" t="n">
-        <v>1861.78</v>
+        <v>1849.86</v>
       </c>
     </row>
     <row r="614">
@@ -37905,7 +37905,7 @@
         </is>
       </c>
       <c r="M614" s="2" t="n">
-        <v>3979.1</v>
+        <v>3953.61</v>
       </c>
     </row>
     <row r="615">
@@ -37966,7 +37966,7 @@
         </is>
       </c>
       <c r="M615" s="2" t="n">
-        <v>7619.76</v>
+        <v>7570.95</v>
       </c>
     </row>
     <row r="616">
@@ -38027,7 +38027,7 @@
         </is>
       </c>
       <c r="M616" s="2" t="n">
-        <v>2234.98</v>
+        <v>2220.66</v>
       </c>
     </row>
     <row r="617">
@@ -38088,7 +38088,7 @@
         </is>
       </c>
       <c r="M617" s="2" t="n">
-        <v>3074.75</v>
+        <v>3055.05</v>
       </c>
     </row>
     <row r="618">
@@ -38149,7 +38149,7 @@
         </is>
       </c>
       <c r="M618" s="2" t="n">
-        <v>4668.68</v>
+        <v>4638.77</v>
       </c>
     </row>
     <row r="619">
@@ -38210,7 +38210,7 @@
         </is>
       </c>
       <c r="M619" s="2" t="n">
-        <v>1236.96</v>
+        <v>1229.04</v>
       </c>
     </row>
     <row r="620">
@@ -38271,7 +38271,7 @@
         </is>
       </c>
       <c r="M620" s="2" t="n">
-        <v>21328.4</v>
+        <v>21191.76</v>
       </c>
     </row>
     <row r="621">
@@ -38332,7 +38332,7 @@
         </is>
       </c>
       <c r="M621" s="2" t="n">
-        <v>1140.52</v>
+        <v>1133.21</v>
       </c>
     </row>
     <row r="622">
@@ -38393,7 +38393,7 @@
         </is>
       </c>
       <c r="M622" s="2" t="n">
-        <v>1293.67</v>
+        <v>1285.38</v>
       </c>
     </row>
     <row r="623">
@@ -38454,7 +38454,7 @@
         </is>
       </c>
       <c r="M623" s="2" t="n">
-        <v>9791.860000000001</v>
+        <v>9729.129999999999</v>
       </c>
     </row>
     <row r="624">
@@ -38515,7 +38515,7 @@
         </is>
       </c>
       <c r="M624" s="2" t="n">
-        <v>935.92</v>
+        <v>929.9299999999999</v>
       </c>
     </row>
     <row r="625">
@@ -38576,7 +38576,7 @@
         </is>
       </c>
       <c r="M625" s="2" t="n">
-        <v>1052.55</v>
+        <v>1045.81</v>
       </c>
     </row>
     <row r="626">
@@ -38637,7 +38637,7 @@
         </is>
       </c>
       <c r="M626" s="2" t="n">
-        <v>1481.79</v>
+        <v>1472.3</v>
       </c>
     </row>
     <row r="627">
@@ -38698,7 +38698,7 @@
         </is>
       </c>
       <c r="M627" s="2" t="n">
-        <v>4942.31</v>
+        <v>4910.65</v>
       </c>
     </row>
     <row r="628">
@@ -38759,7 +38759,7 @@
         </is>
       </c>
       <c r="M628" s="2" t="n">
-        <v>777.8</v>
+        <v>772.8200000000001</v>
       </c>
     </row>
     <row r="629">
@@ -38820,7 +38820,7 @@
         </is>
       </c>
       <c r="M629" s="2" t="n">
-        <v>1409.2</v>
+        <v>1400.18</v>
       </c>
     </row>
     <row r="630">
@@ -38881,7 +38881,7 @@
         </is>
       </c>
       <c r="M630" s="2" t="n">
-        <v>2221.18</v>
+        <v>2206.95</v>
       </c>
     </row>
     <row r="631">
@@ -38942,7 +38942,7 @@
         </is>
       </c>
       <c r="M631" s="2" t="n">
-        <v>769.29</v>
+        <v>764.36</v>
       </c>
     </row>
     <row r="632">
@@ -39003,7 +39003,7 @@
         </is>
       </c>
       <c r="M632" s="2" t="n">
-        <v>13639.12</v>
+        <v>13580.37</v>
       </c>
     </row>
     <row r="633">
@@ -39064,7 +39064,7 @@
         </is>
       </c>
       <c r="M633" s="2" t="n">
-        <v>3293.81</v>
+        <v>3279.62</v>
       </c>
     </row>
     <row r="634">
@@ -39125,7 +39125,7 @@
         </is>
       </c>
       <c r="M634" s="2" t="n">
-        <v>4788.69</v>
+        <v>4768.06</v>
       </c>
     </row>
     <row r="635">
@@ -39186,7 +39186,7 @@
         </is>
       </c>
       <c r="M635" s="2" t="n">
-        <v>772.64</v>
+        <v>769.3099999999999</v>
       </c>
     </row>
     <row r="636">
@@ -39247,7 +39247,7 @@
         </is>
       </c>
       <c r="M636" s="2" t="n">
-        <v>1105.65</v>
+        <v>1100.89</v>
       </c>
     </row>
     <row r="637">
@@ -39308,7 +39308,7 @@
         </is>
       </c>
       <c r="M637" s="2" t="n">
-        <v>831.33</v>
+        <v>827.75</v>
       </c>
     </row>
     <row r="638">
@@ -39369,7 +39369,7 @@
         </is>
       </c>
       <c r="M638" s="2" t="n">
-        <v>1098.35</v>
+        <v>1093.62</v>
       </c>
     </row>
     <row r="639">
@@ -39430,7 +39430,7 @@
         </is>
       </c>
       <c r="M639" s="2" t="n">
-        <v>875.22</v>
+        <v>871.45</v>
       </c>
     </row>
     <row r="640">
@@ -39491,7 +39491,7 @@
         </is>
       </c>
       <c r="M640" s="2" t="n">
-        <v>877.1799999999999</v>
+        <v>873.4</v>
       </c>
     </row>
     <row r="641">
@@ -39552,7 +39552,7 @@
         </is>
       </c>
       <c r="M641" s="2" t="n">
-        <v>1735.45</v>
+        <v>1727.97</v>
       </c>
     </row>
     <row r="642">
@@ -39613,7 +39613,7 @@
         </is>
       </c>
       <c r="M642" s="2" t="n">
-        <v>4531.69</v>
+        <v>4512.16</v>
       </c>
     </row>
     <row r="643">
@@ -39674,7 +39674,7 @@
         </is>
       </c>
       <c r="M643" s="2" t="n">
-        <v>19774.92</v>
+        <v>19689.73</v>
       </c>
     </row>
     <row r="644">
@@ -39735,7 +39735,7 @@
         </is>
       </c>
       <c r="M644" s="2" t="n">
-        <v>1218.13</v>
+        <v>1212.88</v>
       </c>
     </row>
     <row r="645">
@@ -39796,7 +39796,7 @@
         </is>
       </c>
       <c r="M645" s="2" t="n">
-        <v>1656.35</v>
+        <v>1649.21</v>
       </c>
     </row>
     <row r="646">
@@ -39857,7 +39857,7 @@
         </is>
       </c>
       <c r="M646" s="2" t="n">
-        <v>5336.91</v>
+        <v>5313.91</v>
       </c>
     </row>
     <row r="647">
@@ -39918,7 +39918,7 @@
         </is>
       </c>
       <c r="M647" s="2" t="n">
-        <v>783.65</v>
+        <v>780.27</v>
       </c>
     </row>
     <row r="648">
@@ -39979,7 +39979,7 @@
         </is>
       </c>
       <c r="M648" s="2" t="n">
-        <v>3857.22</v>
+        <v>3840.6</v>
       </c>
     </row>
     <row r="649">
@@ -40040,7 +40040,7 @@
         </is>
       </c>
       <c r="M649" s="2" t="n">
-        <v>2204.37</v>
+        <v>2194.88</v>
       </c>
     </row>
     <row r="650">
@@ -40101,7 +40101,7 @@
         </is>
       </c>
       <c r="M650" s="2" t="n">
-        <v>1227.81</v>
+        <v>1222.52</v>
       </c>
     </row>
     <row r="651">
@@ -40162,7 +40162,7 @@
         </is>
       </c>
       <c r="M651" s="2" t="n">
-        <v>2256.6</v>
+        <v>2246.87</v>
       </c>
     </row>
     <row r="652">
@@ -40223,7 +40223,7 @@
         </is>
       </c>
       <c r="M652" s="2" t="n">
-        <v>13978.26</v>
+        <v>13918.04</v>
       </c>
     </row>
     <row r="653">
@@ -40284,7 +40284,7 @@
         </is>
       </c>
       <c r="M653" s="2" t="n">
-        <v>782.0599999999999</v>
+        <v>778.6900000000001</v>
       </c>
     </row>
     <row r="654">
@@ -40345,7 +40345,7 @@
         </is>
       </c>
       <c r="M654" s="2" t="n">
-        <v>4394.56</v>
+        <v>4375.63</v>
       </c>
     </row>
     <row r="655">
@@ -40406,7 +40406,7 @@
         </is>
       </c>
       <c r="M655" s="2" t="n">
-        <v>939.6900000000001</v>
+        <v>935.64</v>
       </c>
     </row>
     <row r="656">
@@ -40467,7 +40467,7 @@
         </is>
       </c>
       <c r="M656" s="2" t="n">
-        <v>1637.1</v>
+        <v>1630.04</v>
       </c>
     </row>
     <row r="657">
@@ -40528,7 +40528,7 @@
         </is>
       </c>
       <c r="M657" s="2" t="n">
-        <v>1240.36</v>
+        <v>1235.02</v>
       </c>
     </row>
     <row r="658">
@@ -40589,7 +40589,7 @@
         </is>
       </c>
       <c r="M658" s="2" t="n">
-        <v>2418.42</v>
+        <v>2408.01</v>
       </c>
     </row>
     <row r="659">
@@ -40650,7 +40650,7 @@
         </is>
       </c>
       <c r="M659" s="2" t="n">
-        <v>1861.07</v>
+        <v>1853.05</v>
       </c>
     </row>
     <row r="660">
@@ -40711,7 +40711,7 @@
         </is>
       </c>
       <c r="M660" s="2" t="n">
-        <v>32692.4</v>
+        <v>32551.56</v>
       </c>
     </row>
     <row r="661">
@@ -40772,7 +40772,7 @@
         </is>
       </c>
       <c r="M661" s="2" t="n">
-        <v>1632.47</v>
+        <v>1625.43</v>
       </c>
     </row>
     <row r="662">
@@ -40833,7 +40833,7 @@
         </is>
       </c>
       <c r="M662" s="2" t="n">
-        <v>911.83</v>
+        <v>907.9</v>
       </c>
     </row>
     <row r="663">
@@ -40894,7 +40894,7 @@
         </is>
       </c>
       <c r="M663" s="2" t="n">
-        <v>2086.88</v>
+        <v>2056.69</v>
       </c>
     </row>
     <row r="664">
@@ -40955,7 +40955,7 @@
         </is>
       </c>
       <c r="M664" s="2" t="n">
-        <v>9454.809999999999</v>
+        <v>9318.030000000001</v>
       </c>
     </row>
     <row r="665">
@@ -41016,7 +41016,7 @@
         </is>
       </c>
       <c r="M665" s="2" t="n">
-        <v>1601.08</v>
+        <v>1577.92</v>
       </c>
     </row>
     <row r="666">
@@ -41077,7 +41077,7 @@
         </is>
       </c>
       <c r="M666" s="2" t="n">
-        <v>769.85</v>
+        <v>758.72</v>
       </c>
     </row>
     <row r="667">
@@ -41138,7 +41138,7 @@
         </is>
       </c>
       <c r="M667" s="2" t="n">
-        <v>7346.17</v>
+        <v>7239.89</v>
       </c>
     </row>
     <row r="668">
@@ -41199,7 +41199,7 @@
         </is>
       </c>
       <c r="M668" s="2" t="n">
-        <v>1914.46</v>
+        <v>1886.76</v>
       </c>
     </row>
     <row r="669">
@@ -41260,7 +41260,7 @@
         </is>
       </c>
       <c r="M669" s="2" t="n">
-        <v>4517.82</v>
+        <v>4452.46</v>
       </c>
     </row>
     <row r="670">
@@ -41321,7 +41321,7 @@
         </is>
       </c>
       <c r="M670" s="2" t="n">
-        <v>28851.08</v>
+        <v>28433.69</v>
       </c>
     </row>
     <row r="671">
@@ -41382,7 +41382,7 @@
         </is>
       </c>
       <c r="M671" s="2" t="n">
-        <v>4396.32</v>
+        <v>4332.72</v>
       </c>
     </row>
     <row r="672">
@@ -41443,7 +41443,7 @@
         </is>
       </c>
       <c r="M672" s="2" t="n">
-        <v>940.73</v>
+        <v>927.12</v>
       </c>
     </row>
     <row r="673">
@@ -41504,7 +41504,7 @@
         </is>
       </c>
       <c r="M673" s="2" t="n">
-        <v>3845.3</v>
+        <v>3789.67</v>
       </c>
     </row>
     <row r="674">
@@ -41565,7 +41565,7 @@
         </is>
       </c>
       <c r="M674" s="2" t="n">
-        <v>952.11</v>
+        <v>938.34</v>
       </c>
     </row>
     <row r="675">
@@ -41626,7 +41626,7 @@
         </is>
       </c>
       <c r="M675" s="2" t="n">
-        <v>1008.38</v>
+        <v>993.79</v>
       </c>
     </row>
     <row r="676">
@@ -41687,7 +41687,7 @@
         </is>
       </c>
       <c r="M676" s="2" t="n">
-        <v>2450.81</v>
+        <v>2415.35</v>
       </c>
     </row>
     <row r="677">
@@ -41748,7 +41748,7 @@
         </is>
       </c>
       <c r="M677" s="2" t="n">
-        <v>1622.78</v>
+        <v>1599.3</v>
       </c>
     </row>
     <row r="678">
@@ -41809,7 +41809,7 @@
         </is>
       </c>
       <c r="M678" s="2" t="n">
-        <v>851.83</v>
+        <v>839.51</v>
       </c>
     </row>
     <row r="679">
@@ -41870,7 +41870,7 @@
         </is>
       </c>
       <c r="M679" s="2" t="n">
-        <v>1600.86</v>
+        <v>1577.7</v>
       </c>
     </row>
     <row r="680">
@@ -41931,7 +41931,7 @@
         </is>
       </c>
       <c r="M680" s="2" t="n">
-        <v>5498.97</v>
+        <v>5419.41</v>
       </c>
     </row>
     <row r="681">
@@ -41992,7 +41992,7 @@
         </is>
       </c>
       <c r="M681" s="2" t="n">
-        <v>1224.15</v>
+        <v>1206.44</v>
       </c>
     </row>
     <row r="682">
@@ -42053,7 +42053,7 @@
         </is>
       </c>
       <c r="M682" s="2" t="n">
-        <v>1099.06</v>
+        <v>1083.16</v>
       </c>
     </row>
     <row r="683">
@@ -42114,7 +42114,7 @@
         </is>
       </c>
       <c r="M683" s="2" t="n">
-        <v>12203.77</v>
+        <v>12027.22</v>
       </c>
     </row>
     <row r="684">
@@ -42175,7 +42175,7 @@
         </is>
       </c>
       <c r="M684" s="2" t="n">
-        <v>4737.67</v>
+        <v>4669.13</v>
       </c>
     </row>
     <row r="685">
@@ -42236,7 +42236,7 @@
         </is>
       </c>
       <c r="M685" s="2" t="n">
-        <v>1426.45</v>
+        <v>1405.81</v>
       </c>
     </row>
     <row r="686">
@@ -42297,7 +42297,7 @@
         </is>
       </c>
       <c r="M686" s="2" t="n">
-        <v>775.03</v>
+        <v>763.8200000000001</v>
       </c>
     </row>
     <row r="687">
@@ -42358,7 +42358,7 @@
         </is>
       </c>
       <c r="M687" s="2" t="n">
-        <v>1612.59</v>
+        <v>1589.26</v>
       </c>
     </row>
     <row r="688">
@@ -42419,7 +42419,7 @@
         </is>
       </c>
       <c r="M688" s="2" t="n">
-        <v>9121.530000000001</v>
+        <v>8989.559999999999</v>
       </c>
     </row>
     <row r="689">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="M689" s="2" t="n">
-        <v>4691.71</v>
+        <v>4623.84</v>
       </c>
     </row>
     <row r="690">
@@ -42541,7 +42541,7 @@
         </is>
       </c>
       <c r="M690" s="2" t="n">
-        <v>1252.26</v>
+        <v>1234.15</v>
       </c>
     </row>
     <row r="691">
@@ -42602,7 +42602,7 @@
         </is>
       </c>
       <c r="M691" s="2" t="n">
-        <v>9024.530000000001</v>
+        <v>8893.969999999999</v>
       </c>
     </row>
     <row r="692">
@@ -42663,7 +42663,7 @@
         </is>
       </c>
       <c r="M692" s="2" t="n">
-        <v>4859.76</v>
+        <v>4789.45</v>
       </c>
     </row>
     <row r="693">
@@ -42724,7 +42724,7 @@
         </is>
       </c>
       <c r="M693" s="2" t="n">
-        <v>1210.59</v>
+        <v>1193.08</v>
       </c>
     </row>
     <row r="694">
@@ -42785,7 +42785,7 @@
         </is>
       </c>
       <c r="M694" s="2" t="n">
-        <v>1216.66</v>
+        <v>1199.06</v>
       </c>
     </row>
     <row r="695">
@@ -42846,7 +42846,7 @@
         </is>
       </c>
       <c r="M695" s="2" t="n">
-        <v>4077.37</v>
+        <v>4018.38</v>
       </c>
     </row>
     <row r="696">
@@ -42907,7 +42907,7 @@
         </is>
       </c>
       <c r="M696" s="2" t="n">
-        <v>2003.78</v>
+        <v>1974.8</v>
       </c>
     </row>
     <row r="697">
@@ -42968,7 +42968,7 @@
         </is>
       </c>
       <c r="M697" s="2" t="n">
-        <v>15804.43</v>
+        <v>15575.79</v>
       </c>
     </row>
     <row r="698">
@@ -43029,7 +43029,7 @@
         </is>
       </c>
       <c r="M698" s="2" t="n">
-        <v>1271.93</v>
+        <v>1253.52</v>
       </c>
     </row>
     <row r="699">
@@ -43090,7 +43090,7 @@
         </is>
       </c>
       <c r="M699" s="2" t="n">
-        <v>2568.5</v>
+        <v>2531.34</v>
       </c>
     </row>
     <row r="700">
@@ -43151,7 +43151,7 @@
         </is>
       </c>
       <c r="M700" s="2" t="n">
-        <v>1787.56</v>
+        <v>1761.7</v>
       </c>
     </row>
     <row r="701">
@@ -43212,7 +43212,7 @@
         </is>
       </c>
       <c r="M701" s="2" t="n">
-        <v>3534.32</v>
+        <v>3483.19</v>
       </c>
     </row>
     <row r="702">
@@ -43273,7 +43273,7 @@
         </is>
       </c>
       <c r="M702" s="2" t="n">
-        <v>1255.86</v>
+        <v>1237.69</v>
       </c>
     </row>
     <row r="703">
@@ -43334,7 +43334,7 @@
         </is>
       </c>
       <c r="M703" s="2" t="n">
-        <v>3091.79</v>
+        <v>3047.06</v>
       </c>
     </row>
     <row r="704">
@@ -43395,7 +43395,7 @@
         </is>
       </c>
       <c r="M704" s="2" t="n">
-        <v>1462.79</v>
+        <v>1441.63</v>
       </c>
     </row>
     <row r="705">
@@ -43456,7 +43456,7 @@
         </is>
       </c>
       <c r="M705" s="2" t="n">
-        <v>1033.55</v>
+        <v>1018.6</v>
       </c>
     </row>
     <row r="706">
@@ -43517,7 +43517,7 @@
         </is>
       </c>
       <c r="M706" s="2" t="n">
-        <v>1352.49</v>
+        <v>1323.4</v>
       </c>
     </row>
     <row r="707">
@@ -43578,7 +43578,7 @@
         </is>
       </c>
       <c r="M707" s="2" t="n">
-        <v>1851.99</v>
+        <v>1812.14</v>
       </c>
     </row>
     <row r="708">
@@ -43639,7 +43639,7 @@
         </is>
       </c>
       <c r="M708" s="2" t="n">
-        <v>1234.78</v>
+        <v>1208.22</v>
       </c>
     </row>
     <row r="709">
@@ -43700,7 +43700,7 @@
         </is>
       </c>
       <c r="M709" s="2" t="n">
-        <v>1908.67</v>
+        <v>1867.61</v>
       </c>
     </row>
     <row r="710">
@@ -43761,7 +43761,7 @@
         </is>
       </c>
       <c r="M710" s="2" t="n">
-        <v>1390.63</v>
+        <v>1360.71</v>
       </c>
     </row>
     <row r="711">
@@ -43822,7 +43822,7 @@
         </is>
       </c>
       <c r="M711" s="2" t="n">
-        <v>1731.93</v>
+        <v>1694.67</v>
       </c>
     </row>
     <row r="712">
@@ -43883,7 +43883,7 @@
         </is>
       </c>
       <c r="M712" s="2" t="n">
-        <v>3411.57</v>
+        <v>3338.17</v>
       </c>
     </row>
     <row r="713">
@@ -43944,7 +43944,7 @@
         </is>
       </c>
       <c r="M713" s="2" t="n">
-        <v>1385.6</v>
+        <v>1355.79</v>
       </c>
     </row>
     <row r="714">
@@ -44005,7 +44005,7 @@
         </is>
       </c>
       <c r="M714" s="2" t="n">
-        <v>4394.36</v>
+        <v>4299.82</v>
       </c>
     </row>
     <row r="715">
@@ -44066,7 +44066,7 @@
         </is>
       </c>
       <c r="M715" s="2" t="n">
-        <v>3352.04</v>
+        <v>3279.92</v>
       </c>
     </row>
     <row r="716">
@@ -44127,7 +44127,7 @@
         </is>
       </c>
       <c r="M716" s="2" t="n">
-        <v>2768.06</v>
+        <v>2708.51</v>
       </c>
     </row>
     <row r="717">
@@ -44188,7 +44188,7 @@
         </is>
       </c>
       <c r="M717" s="2" t="n">
-        <v>1322.62</v>
+        <v>1294.17</v>
       </c>
     </row>
     <row r="718">
@@ -44249,7 +44249,7 @@
         </is>
       </c>
       <c r="M718" s="2" t="n">
-        <v>2167.69</v>
+        <v>2121.05</v>
       </c>
     </row>
     <row r="719">
@@ -44310,7 +44310,7 @@
         </is>
       </c>
       <c r="M719" s="2" t="n">
-        <v>921.61</v>
+        <v>901.78</v>
       </c>
     </row>
     <row r="720">
@@ -44371,7 +44371,7 @@
         </is>
       </c>
       <c r="M720" s="2" t="n">
-        <v>10340.23</v>
+        <v>10117.76</v>
       </c>
     </row>
     <row r="721">
@@ -44432,7 +44432,7 @@
         </is>
       </c>
       <c r="M721" s="2" t="n">
-        <v>2597.39</v>
+        <v>2541.51</v>
       </c>
     </row>
     <row r="722">
@@ -44493,7 +44493,7 @@
         </is>
       </c>
       <c r="M722" s="2" t="n">
-        <v>1673.29</v>
+        <v>1637.29</v>
       </c>
     </row>
     <row r="723">
@@ -44554,7 +44554,7 @@
         </is>
       </c>
       <c r="M723" s="2" t="n">
-        <v>9855.719999999999</v>
+        <v>9643.67</v>
       </c>
     </row>
     <row r="724">
@@ -44615,7 +44615,7 @@
         </is>
       </c>
       <c r="M724" s="2" t="n">
-        <v>1413.51</v>
+        <v>1383.1</v>
       </c>
     </row>
     <row r="725">
@@ -44676,7 +44676,7 @@
         </is>
       </c>
       <c r="M725" s="2" t="n">
-        <v>804.75</v>
+        <v>787.4400000000001</v>
       </c>
     </row>
     <row r="726">
@@ -44737,7 +44737,7 @@
         </is>
       </c>
       <c r="M726" s="2" t="n">
-        <v>12839.82</v>
+        <v>12563.57</v>
       </c>
     </row>
     <row r="727">
@@ -44798,7 +44798,7 @@
         </is>
       </c>
       <c r="M727" s="2" t="n">
-        <v>2113.48</v>
+        <v>2068.01</v>
       </c>
     </row>
     <row r="728">
@@ -44859,7 +44859,7 @@
         </is>
       </c>
       <c r="M728" s="2" t="n">
-        <v>791.35</v>
+        <v>774.33</v>
       </c>
     </row>
     <row r="729">
@@ -44920,7 +44920,7 @@
         </is>
       </c>
       <c r="M729" s="2" t="n">
-        <v>1841.48</v>
+        <v>1801.86</v>
       </c>
     </row>
     <row r="730">
@@ -44981,7 +44981,7 @@
         </is>
       </c>
       <c r="M730" s="2" t="n">
-        <v>6022.41</v>
+        <v>5892.84</v>
       </c>
     </row>
     <row r="731">
@@ -45042,7 +45042,7 @@
         </is>
       </c>
       <c r="M731" s="2" t="n">
-        <v>1417.21</v>
+        <v>1386.72</v>
       </c>
     </row>
     <row r="732">
@@ -45103,7 +45103,7 @@
         </is>
       </c>
       <c r="M732" s="2" t="n">
-        <v>1253.44</v>
+        <v>1224.27</v>
       </c>
     </row>
     <row r="733">
@@ -45164,7 +45164,7 @@
         </is>
       </c>
       <c r="M733" s="2" t="n">
-        <v>29100.26</v>
+        <v>28423.13</v>
       </c>
     </row>
     <row r="734">
@@ -45225,7 +45225,7 @@
         </is>
       </c>
       <c r="M734" s="2" t="n">
-        <v>873.9</v>
+        <v>853.5700000000001</v>
       </c>
     </row>
     <row r="735">
@@ -45286,7 +45286,7 @@
         </is>
       </c>
       <c r="M735" s="2" t="n">
-        <v>12714.22</v>
+        <v>12418.37</v>
       </c>
     </row>
     <row r="736">
@@ -45347,7 +45347,7 @@
         </is>
       </c>
       <c r="M736" s="2" t="n">
-        <v>2015.32</v>
+        <v>1968.43</v>
       </c>
     </row>
     <row r="737">
@@ -45408,7 +45408,7 @@
         </is>
       </c>
       <c r="M737" s="2" t="n">
-        <v>1299.5</v>
+        <v>1269.26</v>
       </c>
     </row>
     <row r="738">
@@ -45469,7 +45469,7 @@
         </is>
       </c>
       <c r="M738" s="2" t="n">
-        <v>17052.35</v>
+        <v>16655.55</v>
       </c>
     </row>
     <row r="739">
@@ -45530,7 +45530,7 @@
         </is>
       </c>
       <c r="M739" s="2" t="n">
-        <v>9711.65</v>
+        <v>9485.67</v>
       </c>
     </row>
     <row r="740">
@@ -45591,7 +45591,7 @@
         </is>
       </c>
       <c r="M740" s="2" t="n">
-        <v>3464.1</v>
+        <v>3383.5</v>
       </c>
     </row>
     <row r="741">
@@ -45652,7 +45652,7 @@
         </is>
       </c>
       <c r="M741" s="2" t="n">
-        <v>1264.34</v>
+        <v>1234.92</v>
       </c>
     </row>
     <row r="742">
@@ -45713,7 +45713,7 @@
         </is>
       </c>
       <c r="M742" s="2" t="n">
-        <v>32505.25</v>
+        <v>31748.88</v>
       </c>
     </row>
     <row r="743">
@@ -45774,7 +45774,7 @@
         </is>
       </c>
       <c r="M743" s="2" t="n">
-        <v>1481.63</v>
+        <v>1447.16</v>
       </c>
     </row>
     <row r="744">
@@ -45835,7 +45835,7 @@
         </is>
       </c>
       <c r="M744" s="2" t="n">
-        <v>1477.89</v>
+        <v>1443.51</v>
       </c>
     </row>
     <row r="745">
@@ -45896,7 +45896,7 @@
         </is>
       </c>
       <c r="M745" s="2" t="n">
-        <v>1765.72</v>
+        <v>1724.64</v>
       </c>
     </row>
     <row r="746">
@@ -45957,7 +45957,7 @@
         </is>
       </c>
       <c r="M746" s="2" t="n">
-        <v>5238.11</v>
+        <v>5116.22</v>
       </c>
     </row>
     <row r="747">
@@ -46018,7 +46018,7 @@
         </is>
       </c>
       <c r="M747" s="2" t="n">
-        <v>771.47</v>
+        <v>753.52</v>
       </c>
     </row>
     <row r="748">
@@ -46079,7 +46079,7 @@
         </is>
       </c>
       <c r="M748" s="2" t="n">
-        <v>1843.28</v>
+        <v>1800.39</v>
       </c>
     </row>
     <row r="749">
@@ -46140,7 +46140,7 @@
         </is>
       </c>
       <c r="M749" s="2" t="n">
-        <v>1603.92</v>
+        <v>1566.6</v>
       </c>
     </row>
     <row r="750">
@@ -46201,7 +46201,7 @@
         </is>
       </c>
       <c r="M750" s="2" t="n">
-        <v>1051.12</v>
+        <v>1026.66</v>
       </c>
     </row>
     <row r="751">
@@ -46262,7 +46262,7 @@
         </is>
       </c>
       <c r="M751" s="2" t="n">
-        <v>8476.93</v>
+        <v>8279.68</v>
       </c>
     </row>
     <row r="752">
@@ -46323,7 +46323,7 @@
         </is>
       </c>
       <c r="M752" s="2" t="n">
-        <v>5107.42</v>
+        <v>4988.57</v>
       </c>
     </row>
     <row r="753">
@@ -46384,7 +46384,7 @@
         </is>
       </c>
       <c r="M753" s="2" t="n">
-        <v>2404.34</v>
+        <v>2348.4</v>
       </c>
     </row>
     <row r="754">
@@ -46445,7 +46445,7 @@
         </is>
       </c>
       <c r="M754" s="2" t="n">
-        <v>801.42</v>
+        <v>782.77</v>
       </c>
     </row>
     <row r="755">
@@ -46506,7 +46506,7 @@
         </is>
       </c>
       <c r="M755" s="2" t="n">
-        <v>5703.12</v>
+        <v>5570.42</v>
       </c>
     </row>
     <row r="756">
@@ -46567,7 +46567,7 @@
         </is>
       </c>
       <c r="M756" s="2" t="n">
-        <v>2149.77</v>
+        <v>2099.75</v>
       </c>
     </row>
     <row r="757">
@@ -46628,7 +46628,7 @@
         </is>
       </c>
       <c r="M757" s="2" t="n">
-        <v>790.62</v>
+        <v>772.22</v>
       </c>
     </row>
     <row r="758">
@@ -46689,7 +46689,7 @@
         </is>
       </c>
       <c r="M758" s="2" t="n">
-        <v>1573.55</v>
+        <v>1536.94</v>
       </c>
     </row>
     <row r="759">
@@ -46750,7 +46750,7 @@
         </is>
       </c>
       <c r="M759" s="2" t="n">
-        <v>15754.31</v>
+        <v>15387.72</v>
       </c>
     </row>
     <row r="760">
@@ -46811,7 +46811,7 @@
         </is>
       </c>
       <c r="M760" s="2" t="n">
-        <v>2284.67</v>
+        <v>2231.51</v>
       </c>
     </row>
     <row r="761">
@@ -46872,7 +46872,7 @@
         </is>
       </c>
       <c r="M761" s="2" t="n">
-        <v>880.34</v>
+        <v>859.85</v>
       </c>
     </row>
     <row r="762">
@@ -46933,7 +46933,7 @@
         </is>
       </c>
       <c r="M762" s="2" t="n">
-        <v>1510.16</v>
+        <v>1475.02</v>
       </c>
     </row>
     <row r="763">
@@ -46994,7 +46994,7 @@
         </is>
       </c>
       <c r="M763" s="2" t="n">
-        <v>1806.14</v>
+        <v>1764.11</v>
       </c>
     </row>
     <row r="764">
@@ -47055,7 +47055,7 @@
         </is>
       </c>
       <c r="M764" s="2" t="n">
-        <v>2831.31</v>
+        <v>2765.43</v>
       </c>
     </row>
     <row r="765">
@@ -47116,7 +47116,7 @@
         </is>
       </c>
       <c r="M765" s="2" t="n">
-        <v>1269.03</v>
+        <v>1239.5</v>
       </c>
     </row>
     <row r="766">
@@ -47177,7 +47177,7 @@
         </is>
       </c>
       <c r="M766" s="2" t="n">
-        <v>3718.42</v>
+        <v>3631.9</v>
       </c>
     </row>
     <row r="767">
@@ -47238,7 +47238,7 @@
         </is>
       </c>
       <c r="M767" s="2" t="n">
-        <v>10080.01</v>
+        <v>9845.450000000001</v>
       </c>
     </row>
     <row r="768">
@@ -47299,7 +47299,7 @@
         </is>
       </c>
       <c r="M768" s="2" t="n">
-        <v>5710.52</v>
+        <v>5577.64</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC mar-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10553,7 +10553,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11529,7 +11529,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13298,7 +13298,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13420,7 +13420,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14522,7 +14522,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15925,7 +15925,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20195,7 +20195,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21781,7 +21781,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -26417,7 +26417,7 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I426" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32822,7 +32822,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -33005,7 +33005,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -36543,7 +36543,7 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I592" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39898,7 +39898,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -40020,7 +40020,7 @@
       </c>
       <c r="H649" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I649" t="inlineStr">
@@ -40447,7 +40447,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40874,7 +40874,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41545,7 +41545,7 @@
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43680,7 +43680,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44229,7 +44229,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46425,7 +46425,7 @@
       </c>
       <c r="H754" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I754" t="inlineStr">
@@ -46486,7 +46486,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46974,7 +46974,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47218,7 +47218,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hospital de Achao</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Superintendencia de Pensiones</t>
+          <t>SUPERINTENDENCIA DE PENSIONES</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE VITACURA</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Feria Internacional del Aire y del Espacio</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUDAHUEL</t>
+          <t>MUNICIPALIDAD DE PUDAHUEL</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. Campo Militar La Reina</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3594,7 +3594,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SANTIAGO ESTE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección General</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dirección de Educación Municipal</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IMunicipalidad de San Pablo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>CENTRAL ODONTOLOGICA IIA. ZONA NAVAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -8108,12 +8108,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social Lampa</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE LAMPA</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>DIVISION DE SALUD</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES HOSPITAL DE PORVENIR</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>ADM. FINANCIERO DEL SISTEMA DE SALUD DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región Metropiltana de Santiago</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>IVª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Centro de Sangre y Tejidos de Concepcion</t>
+          <t>SERVICIO DE SALUD CONCEPCION</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICE</t>
+          <t>CORPORACION DE DESARROLLO DE LA COMUNA DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13476,7 +13476,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -13598,7 +13598,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -13785,7 +13785,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14273,7 +14273,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -14822,7 +14822,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>SAMU</t>
+          <t>Centro Metropolitano de Atención Prehospitalaria</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14883,7 +14883,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15015,7 +15015,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -15432,7 +15432,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Educación</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16347,7 +16347,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16713,7 +16713,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16835,7 +16835,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17018,7 +17018,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17140,7 +17140,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17262,7 +17262,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Brigada de Inteligencia del Ejército</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública de Los Liberta</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS LIBERTADORES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -17506,7 +17506,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>REG CIVIL E IDENT PUNTA ARENAS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -17933,7 +17933,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -18055,7 +18055,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18238,12 +18238,12 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>DIRECCIÓN DE ADMINISTRACIÓN DE SALUD DAS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE LA PAZ</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18848,7 +18848,7 @@
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -18970,7 +18970,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -18980,7 +18980,7 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
@@ -19153,7 +19153,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SEREMI BIENES NACIONALES ARICA Y PARINACOTA</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20495,7 +20495,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XIV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21105,7 +21105,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21166,7 +21166,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21288,7 +21288,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21603,7 +21603,7 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Hospital de Quellón</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -21776,7 +21776,7 @@
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -21898,7 +21898,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HUALQUI DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE HUALQUI</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -22569,7 +22569,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -22630,7 +22630,7 @@
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. de la División Logística</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -22935,7 +22935,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES DEPTO DE</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23240,7 +23240,7 @@
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23301,7 +23301,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACIONES REGION ARICA-PARINACOTA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23423,7 +23423,7 @@
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -23789,7 +23789,7 @@
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -23860,7 +23860,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J384" t="inlineStr">
@@ -24033,7 +24033,7 @@
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y T</t>
+          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -24277,7 +24277,7 @@
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -24338,7 +24338,7 @@
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -25070,7 +25070,7 @@
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS V ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25192,7 +25192,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -25253,7 +25253,7 @@
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IV ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -25558,7 +25558,7 @@
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS XVI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -25802,7 +25802,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -25924,7 +25924,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Contraloría de la Armada</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -25985,7 +25985,7 @@
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Tribunal de Juicio Oral en lo Penal de Valparaiso</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -26717,7 +26717,7 @@
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -26839,7 +26839,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE PUERTO MONTT</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -27022,7 +27022,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27937,7 +27937,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS II ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28425,7 +28425,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS ZONA SEG PRIV CONTROL ARMAS Y EXPL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28669,7 +28669,7 @@
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
@@ -28730,7 +28730,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -28791,7 +28791,7 @@
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -28852,7 +28852,7 @@
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>ADMINISTRACIÓN ADUANA DE ARICA</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -28913,7 +28913,7 @@
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -29035,7 +29035,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>SEREMI LA ARAUCANIA FONDOS EXTRAPRESUPUESTARIOS</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -29289,7 +29289,7 @@
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
@@ -29767,7 +29767,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -29899,7 +29899,7 @@
       </c>
       <c r="I483" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J483" t="inlineStr">
@@ -30011,7 +30011,7 @@
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -30133,7 +30133,7 @@
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -30255,7 +30255,7 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VI ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -30316,7 +30316,7 @@
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -30499,7 +30499,7 @@
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
@@ -30926,7 +30926,7 @@
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>Juzgado de Familia de Valparaiso</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
@@ -31353,7 +31353,7 @@
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>ESCUELA DE GRUMETES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -31780,7 +31780,7 @@
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>CONSULTORIO MIRAFLORES</t>
+          <t>Consultorio Miraflores</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
@@ -31963,7 +31963,7 @@
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -32024,7 +32024,7 @@
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -32268,7 +32268,7 @@
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
@@ -32329,7 +32329,7 @@
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -32400,7 +32400,7 @@
       </c>
       <c r="I524" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J524" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -32878,7 +32878,7 @@
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -33305,7 +33305,7 @@
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -33366,7 +33366,7 @@
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -33488,7 +33488,7 @@
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -34098,7 +34098,7 @@
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -34159,7 +34159,7 @@
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -34403,7 +34403,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -34464,7 +34464,7 @@
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -34525,7 +34525,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -34769,7 +34769,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Región Metropolitana</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -35501,7 +35501,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -35623,7 +35623,7 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL PADRE ALBERTO HURTADO</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -35684,7 +35684,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -35816,7 +35816,7 @@
       </c>
       <c r="I580" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J580" t="inlineStr">
@@ -36111,7 +36111,7 @@
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -36416,7 +36416,7 @@
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>SLEP MARGA MARGA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
@@ -36538,7 +36538,7 @@
       </c>
       <c r="G592" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H592" t="inlineStr">
@@ -36660,7 +36660,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -36965,7 +36965,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -37026,7 +37026,7 @@
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -37097,7 +37097,7 @@
       </c>
       <c r="I601" t="inlineStr">
         <is>
-          <t>MG Publicidad y Eventos SpA</t>
+          <t>MG PUBLICIDAD Y EVENTOS SPA</t>
         </is>
       </c>
       <c r="J601" t="inlineStr">
@@ -37270,7 +37270,7 @@
       </c>
       <c r="G604" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H604" t="inlineStr">
@@ -37453,7 +37453,7 @@
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>INSTITUTO GEOGRAFICO MILITAR</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="G608" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H608" t="inlineStr">
@@ -37697,7 +37697,7 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NEGRETE DEPARTAMENTO COMUNAL DE EDUCACION</t>
+          <t>I MUNICIPALIDAD DE NEGRETE</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
@@ -37758,7 +37758,7 @@
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -37768,7 +37768,7 @@
       </c>
       <c r="I612" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J612" t="inlineStr">
@@ -37819,7 +37819,7 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Regimiento Logístico N° 1 "Tocopilla"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
@@ -37941,7 +37941,7 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
@@ -38429,7 +38429,7 @@
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -38612,7 +38612,7 @@
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H626" t="inlineStr">
@@ -38734,7 +38734,7 @@
       </c>
       <c r="G628" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLÁS D. EDUCACIÓN</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H628" t="inlineStr">
@@ -39039,7 +39039,7 @@
       </c>
       <c r="G633" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H633" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="G637" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
         </is>
       </c>
       <c r="H637" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="G639" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H639" t="inlineStr">
@@ -39466,7 +39466,7 @@
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
@@ -39476,7 +39476,7 @@
       </c>
       <c r="I640" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J640" t="inlineStr">
@@ -39649,7 +39649,7 @@
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS III ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -39954,7 +39954,7 @@
       </c>
       <c r="G648" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H648" t="inlineStr">
@@ -40513,7 +40513,7 @@
       </c>
       <c r="I657" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J657" t="inlineStr">
@@ -40625,7 +40625,7 @@
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE ARICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -40747,7 +40747,7 @@
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Rancagua</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -41052,7 +41052,7 @@
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL ADUANA DE TALCAHUANO</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
@@ -41174,7 +41174,7 @@
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
@@ -41296,7 +41296,7 @@
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificacion</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
@@ -41357,7 +41357,7 @@
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
@@ -41479,7 +41479,7 @@
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Educación</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -41723,7 +41723,7 @@
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
@@ -41733,7 +41733,7 @@
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>INVERSIONES CORP PREMIER LTDA</t>
+          <t>Inversiones Corp Premier Ltda</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -41906,12 +41906,12 @@
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>DIRECCIÓN REGIONAL DE ÑUBLE DEL SERVICIO DE REGISTRO CIVIL E IDENTIFIC</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42333,7 +42333,7 @@
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
@@ -42394,7 +42394,7 @@
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Comando de Personal</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
@@ -42455,7 +42455,7 @@
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA CAMPO MILITAR PENALOLEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
@@ -42577,7 +42577,7 @@
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
@@ -42882,12 +42882,12 @@
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -43004,12 +43004,12 @@
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -43065,7 +43065,7 @@
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LITUECHE</t>
+          <t>Hospital de Litueche</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
@@ -43126,7 +43126,7 @@
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Hospital de Ancud</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
@@ -43431,7 +43431,7 @@
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
@@ -43492,7 +43492,7 @@
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
@@ -43858,7 +43858,7 @@
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Servicio de Salud Atacama</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
@@ -43980,7 +43980,7 @@
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CERRO NAVIA</t>
+          <t>I.MUNICIPALIDAD DE CERRO NAVIA</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
@@ -44041,7 +44041,7 @@
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS X ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
@@ -44407,7 +44407,7 @@
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
@@ -45078,7 +45078,7 @@
       </c>
       <c r="G732" t="inlineStr">
         <is>
-          <t>Bienes y Servicios</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H732" t="inlineStr">
@@ -45200,7 +45200,7 @@
       </c>
       <c r="G734" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H734" t="inlineStr">
@@ -45688,7 +45688,7 @@
       </c>
       <c r="G742" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS I ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H742" t="inlineStr">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46481,7 +46481,7 @@
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -46669,7 +46669,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46908,7 +46908,7 @@
       </c>
       <c r="G762" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE ESCUELA CABALLERIA QUI</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H762" t="inlineStr">
@@ -46969,7 +46969,7 @@
       </c>
       <c r="G763" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - VIII Zona Bio Bio</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H763" t="inlineStr">
@@ -47030,7 +47030,7 @@
       </c>
       <c r="G764" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H764" t="inlineStr">
@@ -47091,7 +47091,7 @@
       </c>
       <c r="G765" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H765" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
@@ -684,7 +684,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1574,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1639,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1704,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2151,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2216,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2281,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2346,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2411,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2476,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2541,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2606,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2671,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2919,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2984,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3179,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3366,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3622,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3687,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3813,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3878,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3943,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4008,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4138,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4203,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4268,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4333,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4524,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4589,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4654,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4719,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4849,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4975,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5101,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5166,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5292,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5357,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5422,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5487,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5552,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5678,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5743,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5808,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5934,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5999,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6064,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6129,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6194,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6259,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6324,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6389,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6454,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6519,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6584,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6649,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6779,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6909,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6974,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7039,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7104,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7482,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7608,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7673,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7738,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7803,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7868,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +7933,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8193,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8258,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8323,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8449,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8514,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8579,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8644,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8709,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8774,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8839,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +8965,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9091,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9217,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9343,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9408,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9534,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9599,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9664,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9790,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9855,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +9920,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9985,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10111,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10176,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10241,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10306,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10371,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10436,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10562,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10627,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10692,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10757,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +10883,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10948,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11013,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11078,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11143,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11334,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11399,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11464,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11529,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11594,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11659,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11724,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11789,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11854,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11919,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11984,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12049,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12175,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12240,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12305,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12435,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12500,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12565,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12630,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12695,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12760,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13012,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13077,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13142,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13207,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13272,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13337,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13467,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13532,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13597,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13662,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13727,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13792,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +13857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +13922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +13987,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14052,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14117,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14182,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14377,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14442,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14568,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14633,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14698,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +15007,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15072,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15137,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15202,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15267,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15332,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15397,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15527,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15592,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15657,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15844,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15909,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16035,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16100,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16165,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16230,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16295,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16547,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16677,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16864,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16929,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16182,7 +16994,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17059,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17124,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17254,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17319,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17445,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17510,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17575,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17705,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17770,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17835,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17961,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +18087,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18152,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18217,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18282,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18347,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18473,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18538,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17707,7 +18603,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18668,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18733,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18798,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18863,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18928,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18073,7 +18993,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +19058,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19188,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19314,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19440,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19505,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19570,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18744,7 +19696,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19887,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +20013,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19110,7 +20078,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +20143,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20273,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20338,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20403,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20468,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20533,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20598,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20724,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20789,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19842,7 +20854,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20919,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +21049,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +21114,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20147,7 +21179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20330,7 +21366,11 @@
           <t>78.069.505-6</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +21492,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21557,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20574,7 +21622,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21752,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21817,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21882,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20879,7 +21947,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +22012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21184,7 +22260,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22325,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21306,7 +22390,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21367,7 +22455,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21733,7 +22829,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22894,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21855,7 +22959,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21977,7 +23085,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22038,7 +23150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22160,7 +23276,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23341,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23406,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23471,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22404,7 +23536,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23601,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23666,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23792,11 @@
           <t>77.708.749-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23922,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23987,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +24052,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22953,7 +24117,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24182,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24308,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24373,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24625,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24690,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23624,7 +24816,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24881,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23746,7 +24946,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23990,7 +25194,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25259,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25324,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24173,7 +25389,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24234,7 +25454,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25519,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25584,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25649,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25714,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +25779,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25905,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +25970,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +26035,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26100,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26165,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26230,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26356,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25149,7 +26421,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26673,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26921,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +27047,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25881,7 +27173,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27238,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27303,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27368,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27433,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27559,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26308,7 +27624,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26369,7 +27689,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +27754,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26552,7 +27880,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26613,7 +27945,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +28010,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +28075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26796,7 +28140,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28205,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28270,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28335,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27040,7 +28400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27162,7 +28530,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28656,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27345,7 +28721,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27467,7 +28851,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28916,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28981,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27650,7 +29046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29233,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27894,7 +29298,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29363,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29489,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29554,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29619,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29684,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28321,7 +29749,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +29940,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +30005,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +30070,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30135,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30200,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28809,7 +30265,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28870,7 +30330,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30395,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30460,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30525,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29114,7 +30590,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29175,7 +30655,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30720,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29419,7 +30911,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +31037,11 @@
           <t>77.547.399-1</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +31102,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29663,7 +31167,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29846,7 +31354,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31480,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31545,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31610,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31675,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31740,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30273,7 +31805,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31870,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30395,7 +31935,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +32000,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30517,7 +32065,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +32130,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32195,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30700,7 +32260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30883,7 +32455,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32585,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32650,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32715,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31188,7 +32780,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31310,7 +32906,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31371,7 +32971,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31493,7 +33097,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31615,7 +33223,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33349,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33414,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31859,7 +33479,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33544,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33609,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32042,7 +33674,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33739,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +33865,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +34117,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34182,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32713,7 +34373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32774,7 +34438,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32896,7 +34564,11 @@
           <t>78.067.906-9</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +34629,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +34694,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +34759,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +34824,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34889,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34954,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33323,7 +35019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33384,7 +35084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +35149,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35214,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33567,7 +35279,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33628,7 +35344,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33689,7 +35409,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35474,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35539,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33872,7 +35604,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +35669,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +35917,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34238,7 +35982,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +36047,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34360,7 +36112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K556" t="inlineStr"/>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L556" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36177,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34482,7 +36242,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34543,7 +36307,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36372,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36437,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36563,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36628,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34909,7 +36693,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34970,7 +36758,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36823,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +37010,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +37075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37262,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35519,7 +37327,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37392,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37457,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35702,7 +37522,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K578" t="inlineStr"/>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L578" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +37587,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35885,7 +37713,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37778,11 @@
           <t>77.399.254-1</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37904,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37969,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36251,7 +38095,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K587" t="inlineStr"/>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L587" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +38160,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38225,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38290,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36556,7 +38416,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38542,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38607,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38672,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +38798,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38863,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37044,7 +38928,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K600" t="inlineStr"/>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L600" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +38993,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +39058,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +39123,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37288,7 +39188,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39253,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37471,7 +39379,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K607" t="inlineStr"/>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L607" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39444,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37593,7 +39509,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K609" t="inlineStr"/>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L609" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39574,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +39761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37898,7 +39826,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K614" t="inlineStr"/>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L614" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39952,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +40017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +40082,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +40147,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40212,11 @@
           <t>77.723.304-1</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40342,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38447,7 +40407,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K623" t="inlineStr"/>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L623" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40472,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40537,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40602,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40667,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40732,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40797,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40923,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +40988,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +41114,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39240,7 +41240,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K636" t="inlineStr"/>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L636" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39301,7 +41305,11 @@
           <t>77.305.910-1</t>
         </is>
       </c>
-      <c r="K637" t="inlineStr"/>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L637" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39362,7 +41370,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K638" t="inlineStr"/>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L638" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41435,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41561,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +41626,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39667,7 +41691,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41756,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41821,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39850,7 +41886,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K646" t="inlineStr"/>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L646" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41951,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +42016,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +42081,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +42146,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42211,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42276,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40277,7 +42341,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K653" t="inlineStr"/>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L653" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42406,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40399,7 +42471,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K655" t="inlineStr"/>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L655" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40460,7 +42536,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40582,7 +42662,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K658" t="inlineStr"/>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L658" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +42727,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +42792,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40765,7 +42857,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +42922,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +43048,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +43113,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +43178,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43243,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43308,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41314,7 +43438,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K670" t="inlineStr"/>
+      <c r="K670" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L670" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +43503,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41436,7 +43568,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +43698,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41619,7 +43763,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43828,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +43954,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41863,7 +44019,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41924,7 +44084,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K680" t="inlineStr"/>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L680" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +44149,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42046,7 +44214,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K682" t="inlineStr"/>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L682" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44279,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +44466,11 @@
           <t>93.558.000-5</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +44531,11 @@
           <t>77.461.733-7</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +44596,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +44661,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +44726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +44913,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +45043,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42961,7 +45169,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45234,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43083,7 +45299,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K699" t="inlineStr"/>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L699" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45364,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43266,7 +45494,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K702" t="inlineStr"/>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L702" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +45559,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +45624,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43449,7 +45689,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K705" t="inlineStr"/>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L705" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +45754,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +45819,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43632,7 +45884,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43693,7 +45949,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K709" t="inlineStr"/>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L709" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +46014,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +46079,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +46144,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +46209,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46274,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46339,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44120,7 +46404,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +46469,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44242,7 +46534,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +46599,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +46725,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +46790,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44547,7 +46855,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K723" t="inlineStr"/>
+      <c r="K723" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L723" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44669,7 +46981,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K725" t="inlineStr"/>
+      <c r="K725" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L725" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +47046,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +47111,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +47176,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44974,7 +47302,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45096,7 +47428,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K732" t="inlineStr"/>
+      <c r="K732" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L732" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45218,7 +47554,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45279,7 +47619,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K735" t="inlineStr"/>
+      <c r="K735" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L735" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45340,7 +47684,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K736" t="inlineStr"/>
+      <c r="K736" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L736" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +47810,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +47875,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +47940,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +48127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45828,7 +48192,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K744" t="inlineStr"/>
+      <c r="K744" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L744" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45950,7 +48318,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K746" t="inlineStr"/>
+      <c r="K746" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L746" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +48505,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +48570,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46316,7 +48696,11 @@
           <t>77.638.992-7</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46377,7 +48761,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46438,7 +48826,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +48891,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46560,7 +48956,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46682,7 +49082,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46865,7 +49269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46987,7 +49395,11 @@
           <t>96.972.190-2</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47048,7 +49460,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47109,7 +49525,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47170,7 +49590,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K766" t="inlineStr"/>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L766" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47231,7 +49655,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-escritorio-y-papeleria/mar-2026.xlsx
@@ -7454,7 +7454,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -14735,7 +14735,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -26393,7 +26393,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -30432,7 +30432,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -35511,7 +35511,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
@@ -41472,7 +41472,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
@@ -47274,7 +47274,7 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
